--- a/data/blocages.xlsx
+++ b/data/blocages.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Personne 02</t>
+          <t>Personne 01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -476,42 +476,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Personne 03</t>
+          <t>Personne 02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dimanche</t>
+          <t>Samedi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -526,21 +526,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -576,17 +576,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -596,47 +596,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Personne 12</t>
+          <t>Personne 08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Personne 17</t>
+          <t>Personne 13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dimanche</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -646,7 +646,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Personne 19</t>
+          <t>Personne 14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -671,47 +671,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Personne 19</t>
+          <t>Personne 14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Personne 20</t>
+          <t>Personne 17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dimanche</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -721,51 +721,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Personne 21</t>
+          <t>Personne 17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Personne 21</t>
+          <t>Personne 22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dimanche</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -796,22 +796,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Personne 22</t>
+          <t>Personne 24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -826,42 +826,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Personne 24</t>
+          <t>Personne 25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -871,12 +871,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Personne 26</t>
+          <t>Personne 28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Personne 27</t>
+          <t>Personne 36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -921,7 +921,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Personne 27</t>
+          <t>Personne 38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -946,22 +946,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Personne 30</t>
+          <t>Personne 38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -971,22 +971,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Personne 30</t>
+          <t>Personne 39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -996,12 +996,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Personne 32</t>
+          <t>Personne 40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1021,12 +1021,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Personne 32</t>
+          <t>Personne 41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1036,47 +1036,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Personne 33</t>
+          <t>Personne 41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dimanche</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Personne 33</t>
+          <t>Personne 43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1096,22 +1096,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Personne 39</t>
+          <t>Personne 46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1121,22 +1121,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Personne 39</t>
+          <t>Personne 48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1146,22 +1146,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Personne 40</t>
+          <t>Personne 50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1171,12 +1171,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Personne 43</t>
+          <t>Personne 51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1196,47 +1196,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Personne 43</t>
+          <t>Personne 53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Personne 45</t>
+          <t>Personne 53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1246,47 +1246,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Personne 45</t>
+          <t>Personne 55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Personne 59</t>
+          <t>Personne 56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dimanche</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1296,7 +1296,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Personne 61</t>
+          <t>Personne 59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1306,57 +1306,57 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Personne 62</t>
+          <t>Personne 59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Personne 62</t>
+          <t>Personne 69</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1366,181 +1366,6 @@
       </c>
       <c r="E38" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Personne 65</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Personne 65</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Lundi</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Personne 66</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Personne 67</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Personne 67</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Personne 68</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Jeudi</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Personne 68</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/blocages.xlsx
+++ b/data/blocages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FEA98B-A0CC-42CD-98E0-57FDABD73BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F5F8C0-B092-4573-A63D-67748C5F6611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="1" r:id="rId1"/>
@@ -1183,30 +1183,30 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/data/blocages.xlsx
+++ b/data/blocages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F5F8C0-B092-4573-A63D-67748C5F6611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DF625E-C03D-4BCC-9EA6-1660955CB301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="Vendredi" sheetId="4" r:id="rId4"/>
     <sheet name="Samedi" sheetId="5" r:id="rId5"/>
     <sheet name="Dimanche" sheetId="6" r:id="rId6"/>
+    <sheet name="Concerts" sheetId="7" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="116">
   <si>
     <t>Nom</t>
   </si>
@@ -77,7 +78,340 @@
     <t>Fin</t>
   </si>
   <si>
-    <t>Priorité</t>
+    <t>Priorité 1</t>
+  </si>
+  <si>
+    <t>Priorité 2</t>
+  </si>
+  <si>
+    <t>Mardi</t>
+  </si>
+  <si>
+    <t>Mercredi</t>
+  </si>
+  <si>
+    <t>Jeudi</t>
+  </si>
+  <si>
+    <t>Vendredi</t>
+  </si>
+  <si>
+    <t>Samedi</t>
+  </si>
+  <si>
+    <t>Dimanche</t>
+  </si>
+  <si>
+    <t>Suzanne</t>
+  </si>
+  <si>
+    <t>Lorde</t>
+  </si>
+  <si>
+    <t>Twenty One Pilots</t>
+  </si>
+  <si>
+    <t>Sam Sauvage</t>
+  </si>
+  <si>
+    <t>The Last Dinner Party</t>
+  </si>
+  <si>
+    <t>The Cure</t>
+  </si>
+  <si>
+    <t>Disiz</t>
+  </si>
+  <si>
+    <t>Theodora</t>
+  </si>
+  <si>
+    <t>Gorillaz</t>
+  </si>
+  <si>
+    <t>Yamê</t>
+  </si>
+  <si>
+    <t>Keny Arkana</t>
+  </si>
+  <si>
+    <t>Orelsan</t>
+  </si>
+  <si>
+    <t>Adèle Castillon</t>
+  </si>
+  <si>
+    <t>Vanessa Paradis</t>
+  </si>
+  <si>
+    <t>Katy Perry</t>
+  </si>
+  <si>
+    <t>Zaz</t>
+  </si>
+  <si>
+    <t>Gims</t>
+  </si>
+  <si>
+    <t>Timmy Trumpet</t>
+  </si>
+  <si>
+    <t>Balu Brigada</t>
+  </si>
+  <si>
+    <t>Asaf Avidan</t>
+  </si>
+  <si>
+    <t>Perceval</t>
+  </si>
+  <si>
+    <t>The Young Gods</t>
+  </si>
+  <si>
+    <t>Feu! Chatterton</t>
+  </si>
+  <si>
+    <t>Kompromat</t>
+  </si>
+  <si>
+    <t>Miki</t>
+  </si>
+  <si>
+    <t>Morcheeba</t>
+  </si>
+  <si>
+    <t>Buraka Som Sistema</t>
+  </si>
+  <si>
+    <t>Amelie Lens presents AURA</t>
+  </si>
+  <si>
+    <t>Solann</t>
+  </si>
+  <si>
+    <t>Björn Again</t>
+  </si>
+  <si>
+    <t>Julien Clerc</t>
+  </si>
+  <si>
+    <t>Mosimann</t>
+  </si>
+  <si>
+    <t>Marguerite</t>
+  </si>
+  <si>
+    <t>Helena</t>
+  </si>
+  <si>
+    <t>Jok'Air</t>
+  </si>
+  <si>
+    <t>Vald x Vladimir Cauchemar x Todiefor</t>
+  </si>
+  <si>
+    <t>Carmina Burana</t>
+  </si>
+  <si>
+    <t>Luiza</t>
+  </si>
+  <si>
+    <t>Bob Sinclar</t>
+  </si>
+  <si>
+    <t>Club Katel</t>
+  </si>
+  <si>
+    <t>Dylan Dylan</t>
+  </si>
+  <si>
+    <t>okgiorgio</t>
+  </si>
+  <si>
+    <t>Upsilone</t>
+  </si>
+  <si>
+    <t>Bound By Endogamy</t>
+  </si>
+  <si>
+    <t>Zaatar</t>
+  </si>
+  <si>
+    <t>Jen Cardini</t>
+  </si>
+  <si>
+    <t>Kendal</t>
+  </si>
+  <si>
+    <t>Braises de Velours</t>
+  </si>
+  <si>
+    <t>Camille Doe</t>
+  </si>
+  <si>
+    <t>riria</t>
+  </si>
+  <si>
+    <t>Diffrent</t>
+  </si>
+  <si>
+    <t>Estelle Zamme</t>
+  </si>
+  <si>
+    <t>Legit Girl DJ</t>
+  </si>
+  <si>
+    <t>DJ Schnake</t>
+  </si>
+  <si>
+    <t>Urumi</t>
+  </si>
+  <si>
+    <t>Marara Kelly</t>
+  </si>
+  <si>
+    <t>Deize Tigrona &amp; DouceSoeur</t>
+  </si>
+  <si>
+    <t>LinaPary</t>
+  </si>
+  <si>
+    <t>Kabylie Minogue</t>
+  </si>
+  <si>
+    <t>Esaïa</t>
+  </si>
+  <si>
+    <t>Little Lion Sound &amp; Basta Lion</t>
+  </si>
+  <si>
+    <t>Omega Nebula</t>
+  </si>
+  <si>
+    <t>Roni Size</t>
+  </si>
+  <si>
+    <t>Maustetytöt</t>
+  </si>
+  <si>
+    <t>Skald</t>
+  </si>
+  <si>
+    <t>Witch Club Satan</t>
+  </si>
+  <si>
+    <t>Witch Club Satan (2ème)</t>
+  </si>
+  <si>
+    <t>Asgeir</t>
+  </si>
+  <si>
+    <t>Eivør</t>
+  </si>
+  <si>
+    <t>Antti Paalanen</t>
+  </si>
+  <si>
+    <t>Hindarfjäll</t>
+  </si>
+  <si>
+    <t>Steve'N'Seagulls</t>
+  </si>
+  <si>
+    <t>Värttinä</t>
+  </si>
+  <si>
+    <t>Katarina Barruk</t>
+  </si>
+  <si>
+    <t>Eihwar</t>
+  </si>
+  <si>
+    <t>Trolska Polska</t>
+  </si>
+  <si>
+    <t>Tarrak</t>
+  </si>
+  <si>
+    <t>Teksti-TV 666</t>
+  </si>
+  <si>
+    <t>Hialøsa</t>
+  </si>
+  <si>
+    <t>Tuuletar</t>
+  </si>
+  <si>
+    <t>Trolska Polska (2ème)</t>
+  </si>
+  <si>
+    <t>Soft Loft</t>
+  </si>
+  <si>
+    <t>DITTER</t>
+  </si>
+  <si>
+    <t>Sprints</t>
+  </si>
+  <si>
+    <t>Sam Quealy</t>
+  </si>
+  <si>
+    <t>Nonante</t>
+  </si>
+  <si>
+    <t>Sylvie Kreusch</t>
+  </si>
+  <si>
+    <t>Max Baby</t>
+  </si>
+  <si>
+    <t>St Graal</t>
+  </si>
+  <si>
+    <t>Marie Jay</t>
+  </si>
+  <si>
+    <t>Nusantara Beat</t>
+  </si>
+  <si>
+    <t>Joshua Idehen</t>
+  </si>
+  <si>
+    <t>Ino Casablanca</t>
+  </si>
+  <si>
+    <t>Roxane</t>
+  </si>
+  <si>
+    <t>Camille Yembe</t>
+  </si>
+  <si>
+    <t>Sueilo</t>
+  </si>
+  <si>
+    <t>Nashwa</t>
+  </si>
+  <si>
+    <t>ETO</t>
+  </si>
+  <si>
+    <t>La Valentina</t>
+  </si>
+  <si>
+    <t>LinLin</t>
+  </si>
+  <si>
+    <t>Dope Saint Jude</t>
+  </si>
+  <si>
+    <t>Mo'Kalamity</t>
+  </si>
+  <si>
+    <t>Open Season</t>
+  </si>
+  <si>
+    <t>THK</t>
   </si>
 </sst>
 </file>
@@ -121,14 +455,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -860,13 +1249,13 @@
         </row>
         <row r="65">
           <cell r="B65" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="E65" t="str">
-            <v>Delassus</v>
+            <v>Ménard</v>
           </cell>
           <cell r="F65" t="str">
-            <v>Frank</v>
+            <v>Mireille</v>
           </cell>
         </row>
         <row r="66">
@@ -874,10 +1263,10 @@
             <v>0</v>
           </cell>
           <cell r="E66" t="str">
-            <v>Rieger</v>
+            <v>Delassus</v>
           </cell>
           <cell r="F66" t="str">
-            <v>Maya</v>
+            <v>Frank</v>
           </cell>
         </row>
         <row r="67">
@@ -885,10 +1274,10 @@
             <v>0</v>
           </cell>
           <cell r="E67" t="str">
-            <v>Michel</v>
+            <v>Rieger</v>
           </cell>
           <cell r="F67" t="str">
-            <v>Mehdi</v>
+            <v>Maya</v>
           </cell>
         </row>
         <row r="68">
@@ -896,10 +1285,10 @@
             <v>0</v>
           </cell>
           <cell r="E68" t="str">
-            <v>Ménard</v>
+            <v>Michel</v>
           </cell>
           <cell r="F68" t="str">
-            <v>Mireille</v>
+            <v>Mehdi</v>
           </cell>
         </row>
         <row r="69">
@@ -907,10 +1296,10 @@
             <v>0</v>
           </cell>
           <cell r="E69" t="str">
-            <v>Goumaz</v>
+            <v>Pieper</v>
           </cell>
           <cell r="F69" t="str">
-            <v>Alexandre</v>
+            <v>Giulia</v>
           </cell>
         </row>
         <row r="70">
@@ -918,10 +1307,10 @@
             <v>0</v>
           </cell>
           <cell r="E70" t="str">
-            <v>Pieper</v>
+            <v>Durand</v>
           </cell>
           <cell r="F70" t="str">
-            <v>Giulia</v>
+            <v>Isidore</v>
           </cell>
         </row>
         <row r="71">
@@ -929,29 +1318,29 @@
             <v>0</v>
           </cell>
           <cell r="E71" t="str">
-            <v>Durand</v>
+            <v>Lemay</v>
           </cell>
           <cell r="F71" t="str">
-            <v>Isidore</v>
+            <v>Mae</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72" t="b">
             <v>0</v>
           </cell>
-          <cell r="E72" t="str">
-            <v>Lemay</v>
-          </cell>
           <cell r="F72" t="str">
-            <v>Mae</v>
+            <v>Michelle-Evy</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73" t="b">
             <v>0</v>
           </cell>
+          <cell r="E73" t="str">
+            <v>Bonay</v>
+          </cell>
           <cell r="F73" t="str">
-            <v>Michelle-Evy</v>
+            <v>Paul</v>
           </cell>
         </row>
         <row r="74">
@@ -959,10 +1348,10 @@
             <v>0</v>
           </cell>
           <cell r="E74" t="str">
-            <v>Bonay</v>
+            <v>Lagier</v>
           </cell>
           <cell r="F74" t="str">
-            <v>Paul</v>
+            <v>Tician</v>
           </cell>
         </row>
         <row r="75">
@@ -970,10 +1359,10 @@
             <v>0</v>
           </cell>
           <cell r="E75" t="str">
-            <v>Lagier</v>
+            <v>Carrière</v>
           </cell>
           <cell r="F75" t="str">
-            <v>Tician</v>
+            <v>Zellie</v>
           </cell>
         </row>
         <row r="76">
@@ -981,10 +1370,10 @@
             <v>0</v>
           </cell>
           <cell r="E76" t="str">
-            <v>Carrière</v>
+            <v>Goumaz</v>
           </cell>
           <cell r="F76" t="str">
-            <v>Zellie</v>
+            <v>Alexandre</v>
           </cell>
         </row>
         <row r="77">
@@ -1210,6 +1599,96 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31667355-F678-44DA-A09E-12A233EE0EAE}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0">
+  <autoFilter ref="A1:C18" xr:uid="{31667355-F678-44DA-A09E-12A233EE0EAE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C18">
+    <sortCondition ref="A1:A18"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{8E8B93B6-FFFA-43DA-9F4F-50757F0A0BB7}" name="Mardi"/>
+    <tableColumn id="2" xr3:uid="{C48EDA23-1025-4E75-B10E-227DEE82B8BD}" name="Début" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{B5DF4254-9F45-48A8-ABC0-B6F06CA1B9AB}" name="Fin" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{04BE98B2-B85F-4882-BE6E-DCFC0A75118B}" name="Table2" displayName="Table2" ref="D1:F18" totalsRowShown="0">
+  <autoFilter ref="D1:F18" xr:uid="{04BE98B2-B85F-4882-BE6E-DCFC0A75118B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:F18">
+    <sortCondition ref="D1:D18"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{095BD6C4-973C-43C1-80CE-C1A359C07B30}" name="Mercredi"/>
+    <tableColumn id="2" xr3:uid="{94F6012C-3B57-463E-B0C5-19E9BA6495AA}" name="Début" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{4A1A2075-B7E2-42F0-B7D0-601CA6ED90A7}" name="Fin" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B75CB504-E307-4C94-A282-F3FDD49CCC96}" name="Table3" displayName="Table3" ref="G1:I19" totalsRowShown="0">
+  <autoFilter ref="G1:I19" xr:uid="{B75CB504-E307-4C94-A282-F3FDD49CCC96}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:I19">
+    <sortCondition ref="G1:G19"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{4E6D4E23-2332-4B3F-B79A-9DF4ECB8F9E0}" name="Jeudi"/>
+    <tableColumn id="2" xr3:uid="{99E9964E-444F-45E0-AA5E-D53985498927}" name="Début" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{367FB86A-A425-4FA3-9208-03C03A820C10}" name="Fin" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5A5C5630-728A-4A3D-8A83-1E2DEBB42897}" name="Table4" displayName="Table4" ref="J1:L19" totalsRowShown="0">
+  <autoFilter ref="J1:L19" xr:uid="{5A5C5630-728A-4A3D-8A83-1E2DEBB42897}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J2:L19">
+    <sortCondition ref="J1:J19"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{DE30BCE9-F1AF-4C08-B39E-0C9853F3017D}" name="Vendredi"/>
+    <tableColumn id="2" xr3:uid="{A8DF8A9F-F84C-4960-988E-1E980B175AB2}" name="Début" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{A8243E08-6684-40CA-8875-E3059911D8AA}" name="Fin" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{52C6E342-26C5-4169-B364-0750430DCCE4}" name="Table5" displayName="Table5" ref="M1:O19" totalsRowShown="0">
+  <autoFilter ref="M1:O19" xr:uid="{52C6E342-26C5-4169-B364-0750430DCCE4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M2:O19">
+    <sortCondition ref="M1:M19"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{7A71C11D-7C12-40F2-994A-E8B08FF154F3}" name="Samedi"/>
+    <tableColumn id="2" xr3:uid="{193A2EA8-7572-456D-9AF2-8AB7BDAF4FA2}" name="Début" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{7F3E1EDD-55C8-4CB4-A9F7-92D40BA92403}" name="Fin" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{82E67208-45B1-4E00-AF57-DECB223ECABD}" name="Table6" displayName="Table6" ref="P1:R17" totalsRowShown="0">
+  <autoFilter ref="P1:R17" xr:uid="{82E67208-45B1-4E00-AF57-DECB223ECABD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P2:R17">
+    <sortCondition ref="P1:P17"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3F274A3A-E1E0-4299-BDD1-EDE4FB548589}" name="Dimanche"/>
+    <tableColumn id="2" xr3:uid="{79564556-5CF8-4025-B335-FEFC7C6C2FCA}" name="Début" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{1D072B5E-8A60-4C4B-903E-D68DDAC1B33C}" name="Fin" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1497,13 +1976,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1511,518 +1994,1701 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" cm="1">
+        <f t="array" ref="D2:E2">_xlfn.XLOOKUP(C2,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" cm="1">
+        <f t="array" ref="G2:H2">_xlfn.XLOOKUP(F2,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H2" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
         <v>Alegria Lily</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="2" cm="1">
+        <f t="array" ref="D3:E3">_xlfn.XLOOKUP(C3,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.71875</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" cm="1">
+        <f t="array" ref="G3:H3">_xlfn.XLOOKUP(F3,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
         <v>Alexandra</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" cm="1">
+        <f t="array" ref="D4:E4">_xlfn.XLOOKUP(C4,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" cm="1">
+        <f t="array" ref="G4:H4">_xlfn.XLOOKUP(F4,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
         <v>Alice</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" cm="1">
+        <f t="array" ref="D5:E5">_xlfn.XLOOKUP(C5,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" cm="1">
+        <f t="array" ref="G5:H5">_xlfn.XLOOKUP(F5,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
         <v>Analou</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" cm="1">
+        <f t="array" ref="D6:E6">_xlfn.XLOOKUP(C6,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" cm="1">
+        <f t="array" ref="G6:H6">_xlfn.XLOOKUP(F6,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
         <v>Anna</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" cm="1">
+        <f t="array" ref="D7:E7">_xlfn.XLOOKUP(C7,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" cm="1">
+        <f t="array" ref="G7:H7">_xlfn.XLOOKUP(F7,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
         <v>Annouk</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" cm="1">
+        <f t="array" ref="D8:E8">_xlfn.XLOOKUP(C8,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" cm="1">
+        <f t="array" ref="G8:H8">_xlfn.XLOOKUP(F8,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
         <v>Antonin</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" cm="1">
+        <f t="array" ref="D9:E9">_xlfn.XLOOKUP(C9,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="2" cm="1">
+        <f t="array" ref="G9:H9">_xlfn.XLOOKUP(F9,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
         <v>Arsène</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" cm="1">
+        <f t="array" ref="D10:E10">_xlfn.XLOOKUP(C10,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="2" cm="1">
+        <f t="array" ref="G10:H10">_xlfn.XLOOKUP(F10,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
         <v>Arthur</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" cm="1">
+        <f t="array" ref="D11:E11">_xlfn.XLOOKUP(C11,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="2" cm="1">
+        <f t="array" ref="G11:H11">_xlfn.XLOOKUP(F11,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
         <v>Athénaé</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" cm="1">
+        <f t="array" ref="D12:E12">_xlfn.XLOOKUP(C12,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="2" cm="1">
+        <f t="array" ref="G12:H12">_xlfn.XLOOKUP(F12,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.98958333333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
         <v>Auxence</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" cm="1">
+        <f t="array" ref="D13:E13">_xlfn.XLOOKUP(C13,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="2" cm="1">
+        <f t="array" ref="G13:H13">_xlfn.XLOOKUP(F13,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.98958333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
         <v>Ava</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2" cm="1">
+        <f t="array" ref="D14:E14">_xlfn.XLOOKUP(C14,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.86458333333333326</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" cm="1">
+        <f t="array" ref="G14:H14">_xlfn.XLOOKUP(F14,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
         <v>Benoît</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2" cm="1">
+        <f t="array" ref="D15:E15">_xlfn.XLOOKUP(C15,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.86458333333333326</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" cm="1">
+        <f t="array" ref="G15:H15">_xlfn.XLOOKUP(F15,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H15" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
         <v>Corentin</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="2" cm="1">
+        <f t="array" ref="D16:E16">_xlfn.XLOOKUP(C16,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.9375</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" cm="1">
+        <f t="array" ref="G16:H16">_xlfn.XLOOKUP(F16,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H16" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
         <v>Emma</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="2" cm="1">
+        <f t="array" ref="D17:E17">_xlfn.XLOOKUP(C17,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.9375</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2" cm="1">
+        <f t="array" ref="G17:H17">_xlfn.XLOOKUP(F17,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
         <v>Enzo</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2" cm="1">
+        <f t="array" ref="D18:E18">_xlfn.XLOOKUP(C18,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="2" cm="1">
+        <f t="array" ref="G18:H18">_xlfn.XLOOKUP(F18,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
         <v>Eugénie</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="2" cm="1">
+        <f t="array" ref="D19:E19">_xlfn.XLOOKUP(C19,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2" cm="1">
+        <f t="array" ref="G19:H19">_xlfn.XLOOKUP(F19,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H19" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
         <v>Iris</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2" cm="1">
+        <f t="array" ref="D20:E20">_xlfn.XLOOKUP(C20,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" cm="1">
+        <f t="array" ref="G20:H20">_xlfn.XLOOKUP(F20,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
         <v>Jamilah</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" cm="1">
+        <f t="array" ref="D21:E21">_xlfn.XLOOKUP(C21,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E21" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="2" cm="1">
+        <f t="array" ref="G21:H21">_xlfn.XLOOKUP(F21,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
         <v>Jolan</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" cm="1">
+        <f t="array" ref="D22:E22">_xlfn.XLOOKUP(C22,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E22" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="2" cm="1">
+        <f t="array" ref="G22:H22">_xlfn.XLOOKUP(F22,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
         <v xml:space="preserve">Jonas </v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" cm="1">
+        <f t="array" ref="D23:E23">_xlfn.XLOOKUP(C23,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" cm="1">
+        <f t="array" ref="G23:H23">_xlfn.XLOOKUP(F23,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
         <v>Jules</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" cm="1">
+        <f t="array" ref="D24:E24">_xlfn.XLOOKUP(C24,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="2" cm="1">
+        <f t="array" ref="G24:H24">_xlfn.XLOOKUP(F24,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
         <v>Julie</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" cm="1">
+        <f t="array" ref="D25:E25">_xlfn.XLOOKUP(C25,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="2" cm="1">
+        <f t="array" ref="G25:H25">_xlfn.XLOOKUP(F25,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
         <v>Kristel</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="2" cm="1">
+        <f t="array" ref="D26:E26">_xlfn.XLOOKUP(C26,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="2" cm="1">
+        <f t="array" ref="G26:H26">_xlfn.XLOOKUP(F26,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="2" cm="1">
+        <f t="array" ref="D27:E27">_xlfn.XLOOKUP(C27,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E27" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" cm="1">
+        <f t="array" ref="G27:H27">_xlfn.XLOOKUP(F27,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" cm="1">
+        <f t="array" ref="D28:E28">_xlfn.XLOOKUP(C28,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G28" s="2" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.XLOOKUP(F28,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
         <v>Lina-Rosa</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2" cm="1">
+        <f t="array" ref="D29:E29">_xlfn.XLOOKUP(C29,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="2" cm="1">
+        <f t="array" ref="G29:H29">_xlfn.XLOOKUP(F29,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2" cm="1">
+        <f t="array" ref="D30:E30">_xlfn.XLOOKUP(C30,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="2" cm="1">
+        <f t="array" ref="G30:H30">_xlfn.XLOOKUP(F30,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="2" cm="1">
+        <f t="array" ref="D31:E31">_xlfn.XLOOKUP(C31,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="2" cm="1">
+        <f t="array" ref="G31:H31">_xlfn.XLOOKUP(F31,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="2" cm="1">
+        <f t="array" ref="D32:E32">_xlfn.XLOOKUP(C32,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="2" cm="1">
+        <f t="array" ref="G32:H32">_xlfn.XLOOKUP(F32,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <v>Post</v>
       </c>
       <c r="B33" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="2" cm="1">
+        <f t="array" ref="D33:E33">_xlfn.XLOOKUP(C33,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="2" cm="1">
+        <f t="array" ref="G33:H33">_xlfn.XLOOKUP(F33,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H33" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
         <v>Louise</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="2" cm="1">
+        <f t="array" ref="D34:E34">_xlfn.XLOOKUP(C34,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="2" cm="1">
+        <f t="array" ref="G34:H34">_xlfn.XLOOKUP(F34,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H34" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
         <v>Lucas</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="2" cm="1">
+        <f t="array" ref="D35:E35">_xlfn.XLOOKUP(C35,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E35" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="2" cm="1">
+        <f t="array" ref="G35:H35">_xlfn.XLOOKUP(F35,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
         <v>Lucie</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="2" cm="1">
+        <f t="array" ref="D36:E36">_xlfn.XLOOKUP(C36,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G36" s="2" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.XLOOKUP(F36,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
         <v>Maëlan</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="2" cm="1">
+        <f t="array" ref="D37:E37">_xlfn.XLOOKUP(C37,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.8125</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="2" cm="1">
+        <f t="array" ref="G37:H37">_xlfn.XLOOKUP(F37,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
         <v>Maëlle</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="2" cm="1">
+        <f t="array" ref="D38:E38">_xlfn.XLOOKUP(C38,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.8125</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="2" cm="1">
+        <f t="array" ref="G38:H38">_xlfn.XLOOKUP(F38,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
         <v>Marius</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="2" cm="1">
+        <f t="array" ref="D39:E39">_xlfn.XLOOKUP(C39,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="2" cm="1">
+        <f t="array" ref="G39:H39">_xlfn.XLOOKUP(F39,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
         <v>Marot</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D40" s="2" t="str" cm="1">
+        <f t="array" ref="D40">_xlfn.XLOOKUP(C40,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.XLOOKUP(F40,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
         <v>Mathis</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="2" cm="1">
+        <f t="array" ref="D41:E41">_xlfn.XLOOKUP(C41,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="G41" s="2" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.XLOOKUP(F41,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
         <v>Matteo</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="2" cm="1">
+        <f t="array" ref="D42:E42">_xlfn.XLOOKUP(C42,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" s="2" cm="1">
+        <f t="array" ref="G42:H42">_xlfn.XLOOKUP(F42,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H42" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
         <v>Maxime</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="2" cm="1">
+        <f t="array" ref="D43:E43">_xlfn.XLOOKUP(C43,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="2" cm="1">
+        <f t="array" ref="G43:H43">_xlfn.XLOOKUP(F43,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H43" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
         <v>Maya</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="2" cm="1">
+        <f t="array" ref="D44:E44">_xlfn.XLOOKUP(C44,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E44" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="2" cm="1">
+        <f t="array" ref="G44:H44">_xlfn.XLOOKUP(F44,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
         <v>Mickaël</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="2" cm="1">
+        <f t="array" ref="D45:E45">_xlfn.XLOOKUP(C45,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" s="2" cm="1">
+        <f t="array" ref="G45:H45">_xlfn.XLOOKUP(F45,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H45" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
         <v>Morgana</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="2" cm="1">
+        <f t="array" ref="D46:E46">_xlfn.XLOOKUP(C46,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="2" cm="1">
+        <f t="array" ref="G46:H46">_xlfn.XLOOKUP(F46,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H46" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
         <v>Morgane</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="2" cm="1">
+        <f t="array" ref="D47:E47">_xlfn.XLOOKUP(C47,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="2" cm="1">
+        <f t="array" ref="G47:H47">_xlfn.XLOOKUP(F47,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H47" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
         <v>Nathalia</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="2" cm="1">
+        <f t="array" ref="D48:E48">_xlfn.XLOOKUP(C48,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="2" cm="1">
+        <f t="array" ref="G48:H48">_xlfn.XLOOKUP(F48,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H48" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
         <v>Noah</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="2" cm="1">
+        <f t="array" ref="D49:E49">_xlfn.XLOOKUP(C49,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="2" cm="1">
+        <f t="array" ref="G49:H49">_xlfn.XLOOKUP(F49,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H49" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
         <v>Patrick</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D50" s="2" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(C50,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(F50,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
         <v>Rama</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="2" cm="1">
+        <f t="array" ref="D51:E51">_xlfn.XLOOKUP(C51,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="2" cm="1">
+        <f t="array" ref="G51:H51">_xlfn.XLOOKUP(F51,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H51" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
         <v>Raphaël</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="2" cm="1">
+        <f t="array" ref="D52:E52">_xlfn.XLOOKUP(C52,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="2" cm="1">
+        <f t="array" ref="G52:H52">_xlfn.XLOOKUP(F52,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
         <v>Raphaëlle</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="2" cm="1">
+        <f t="array" ref="D53:E53">_xlfn.XLOOKUP(C53,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E53" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="2" cm="1">
+        <f t="array" ref="G53:H53">_xlfn.XLOOKUP(F53,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
         <v>Roxanne</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D54" s="2" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(C54,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(F54,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
         <v>Sébastien</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D55" s="2" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(C55,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(F55,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
         <v>Simon</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D56" s="2" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(C56,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(F56,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
         <v>Theo</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="2" cm="1">
+        <f t="array" ref="D57:E57">_xlfn.XLOOKUP(C57,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E57" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="2" cm="1">
+        <f t="array" ref="G57:H57">_xlfn.XLOOKUP(F57,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H57" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
         <v>Thibault</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="2" cm="1">
+        <f t="array" ref="D58:E58">_xlfn.XLOOKUP(C58,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0.86458333333333326</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="2" cm="1">
+        <f t="array" ref="G58:H58">_xlfn.XLOOKUP(F58,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H58" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
         <v>Titouan</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="2" cm="1">
+        <f t="array" ref="D59:E59">_xlfn.XLOOKUP(C59,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E59" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="2" cm="1">
+        <f t="array" ref="G59:H59">_xlfn.XLOOKUP(F59,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H59" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
         <v>Tristan</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="2" cm="1">
+        <f t="array" ref="D60:E60">_xlfn.XLOOKUP(C60,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="2" cm="1">
+        <f t="array" ref="G60:H60">_xlfn.XLOOKUP(F60,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="H60" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
         <v>Yann</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" cm="1">
+        <f t="array" ref="D61:E61">_xlfn.XLOOKUP(C61,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>0.875</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F61" t="s">
+        <v>32</v>
+      </c>
+      <c r="G61" s="2" cm="1">
+        <f t="array" ref="G61:H61">_xlfn.XLOOKUP(F61,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H61" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
       </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="2" cm="1">
+        <f t="array" ref="D62:E62">_xlfn.XLOOKUP(C62,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="E62" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F62" t="s">
+        <v>32</v>
+      </c>
+      <c r="G62" s="2" cm="1">
+        <f t="array" ref="G62:H62">_xlfn.XLOOKUP(F62,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v>1.0625</v>
+      </c>
+      <c r="H62" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
+      </c>
+      <c r="D63" s="2" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(C63,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(F63,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9ECEB765-3C20-4EAA-8816-9FE357B617C8}">
+          <x14:formula1>
+            <xm:f>Concerts!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C63 F2:F63</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB0BE80-5A54-4435-9512-2BB5720E9EFF}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2030,518 +3696,1047 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D2" s="2" t="str" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(C2,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="str" cm="1">
+        <f t="array" ref="G2">_xlfn.XLOOKUP(F2,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
         <v>Alegria Lily</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D3" s="2" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.XLOOKUP(C3,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.XLOOKUP(F3,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
         <v>Alexandra</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D4" s="2" t="str" cm="1">
+        <f t="array" ref="D4">_xlfn.XLOOKUP(C4,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.XLOOKUP(F4,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
         <v>Alice</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.XLOOKUP(C5,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.XLOOKUP(F5,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
         <v>Analou</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D6" s="2" t="str" cm="1">
+        <f t="array" ref="D6">_xlfn.XLOOKUP(C6,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.XLOOKUP(F6,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
         <v>Anna</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D7" s="2" t="str" cm="1">
+        <f t="array" ref="D7">_xlfn.XLOOKUP(C7,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.XLOOKUP(F7,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
         <v>Annouk</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D8" s="2" t="str" cm="1">
+        <f t="array" ref="D8">_xlfn.XLOOKUP(C8,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.XLOOKUP(F8,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
         <v>Antonin</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D9" s="2" t="str" cm="1">
+        <f t="array" ref="D9">_xlfn.XLOOKUP(C9,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.XLOOKUP(F9,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
         <v>Arsène</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D10" s="2" t="str" cm="1">
+        <f t="array" ref="D10">_xlfn.XLOOKUP(C10,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.XLOOKUP(F10,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
         <v>Arthur</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D11" s="2" t="str" cm="1">
+        <f t="array" ref="D11">_xlfn.XLOOKUP(C11,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.XLOOKUP(F11,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
         <v>Athénaé</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D12" s="2" t="str" cm="1">
+        <f t="array" ref="D12">_xlfn.XLOOKUP(C12,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.XLOOKUP(F12,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
         <v>Auxence</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D13" s="2" t="str" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(C13,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.XLOOKUP(F13,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
         <v>Ava</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D14" s="2" t="str" cm="1">
+        <f t="array" ref="D14">_xlfn.XLOOKUP(C14,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.XLOOKUP(F14,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
         <v>Benoît</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D15" s="2" t="str" cm="1">
+        <f t="array" ref="D15">_xlfn.XLOOKUP(C15,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.XLOOKUP(F15,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
         <v>Corentin</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D16" s="2" t="str" cm="1">
+        <f t="array" ref="D16">_xlfn.XLOOKUP(C16,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.XLOOKUP(F16,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
         <v>Emma</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D17" s="2" t="str" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(C17,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.XLOOKUP(F17,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
         <v>Enzo</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">_xlfn.XLOOKUP(C18,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.XLOOKUP(F18,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
         <v>Eugénie</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">_xlfn.XLOOKUP(C19,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.XLOOKUP(F19,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
         <v>Iris</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D20" s="2" t="str" cm="1">
+        <f t="array" ref="D20">_xlfn.XLOOKUP(C20,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.XLOOKUP(F20,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
         <v>Jamilah</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D21" s="2" t="str" cm="1">
+        <f t="array" ref="D21">_xlfn.XLOOKUP(C21,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.XLOOKUP(F21,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
         <v>Jolan</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D22" s="2" t="str" cm="1">
+        <f t="array" ref="D22">_xlfn.XLOOKUP(C22,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.XLOOKUP(F22,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
         <v xml:space="preserve">Jonas </v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D23" s="2" t="str" cm="1">
+        <f t="array" ref="D23">_xlfn.XLOOKUP(C23,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str" cm="1">
+        <f t="array" ref="G23">_xlfn.XLOOKUP(F23,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
         <v>Jules</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D24" s="2" t="str" cm="1">
+        <f t="array" ref="D24">_xlfn.XLOOKUP(C24,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.XLOOKUP(F24,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
         <v>Julie</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D25" s="2" t="str" cm="1">
+        <f t="array" ref="D25">_xlfn.XLOOKUP(C25,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.XLOOKUP(F25,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
         <v>Kristel</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D26" s="2" t="str" cm="1">
+        <f t="array" ref="D26">_xlfn.XLOOKUP(C26,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str" cm="1">
+        <f t="array" ref="G26">_xlfn.XLOOKUP(F26,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D27" s="2" t="str" cm="1">
+        <f t="array" ref="D27">_xlfn.XLOOKUP(C27,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.XLOOKUP(F27,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D28" s="2" t="str" cm="1">
+        <f t="array" ref="D28">_xlfn.XLOOKUP(C28,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.XLOOKUP(F28,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
         <v>Lina-Rosa</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D29" s="2" t="str" cm="1">
+        <f t="array" ref="D29">_xlfn.XLOOKUP(C29,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str" cm="1">
+        <f t="array" ref="G29">_xlfn.XLOOKUP(F29,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D30" s="2" t="str" cm="1">
+        <f t="array" ref="D30">_xlfn.XLOOKUP(C30,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str" cm="1">
+        <f t="array" ref="G30">_xlfn.XLOOKUP(F30,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D31" s="2" t="str" cm="1">
+        <f t="array" ref="D31">_xlfn.XLOOKUP(C31,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str" cm="1">
+        <f t="array" ref="G31">_xlfn.XLOOKUP(F31,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D32" s="2" t="str" cm="1">
+        <f t="array" ref="D32">_xlfn.XLOOKUP(C32,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str" cm="1">
+        <f t="array" ref="G32">_xlfn.XLOOKUP(F32,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <v>Post</v>
       </c>
       <c r="B33" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D33" s="2" t="str" cm="1">
+        <f t="array" ref="D33">_xlfn.XLOOKUP(C33,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str" cm="1">
+        <f t="array" ref="G33">_xlfn.XLOOKUP(F33,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
         <v>Louise</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">_xlfn.XLOOKUP(C34,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str" cm="1">
+        <f t="array" ref="G34">_xlfn.XLOOKUP(F34,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
         <v>Lucas</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">_xlfn.XLOOKUP(C35,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str" cm="1">
+        <f t="array" ref="G35">_xlfn.XLOOKUP(F35,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
         <v>Lucie</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D36" s="2" t="str" cm="1">
+        <f t="array" ref="D36">_xlfn.XLOOKUP(C36,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.XLOOKUP(F36,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
         <v>Maëlan</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D37" s="2" t="str" cm="1">
+        <f t="array" ref="D37">_xlfn.XLOOKUP(C37,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str" cm="1">
+        <f t="array" ref="G37">_xlfn.XLOOKUP(F37,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
         <v>Maëlle</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D38" s="2" t="str" cm="1">
+        <f t="array" ref="D38">_xlfn.XLOOKUP(C38,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str" cm="1">
+        <f t="array" ref="G38">_xlfn.XLOOKUP(F38,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
         <v>Marius</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D39" s="2" t="str" cm="1">
+        <f t="array" ref="D39">_xlfn.XLOOKUP(C39,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str" cm="1">
+        <f t="array" ref="G39">_xlfn.XLOOKUP(F39,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
         <v>Marot</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D40" s="2" t="str" cm="1">
+        <f t="array" ref="D40">_xlfn.XLOOKUP(C40,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.XLOOKUP(F40,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
         <v>Mathis</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D41" s="2" t="str" cm="1">
+        <f t="array" ref="D41">_xlfn.XLOOKUP(C41,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.XLOOKUP(F41,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
         <v>Matteo</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D42" s="2" t="str" cm="1">
+        <f t="array" ref="D42">_xlfn.XLOOKUP(C42,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.XLOOKUP(F42,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
         <v>Maxime</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D43" s="2" t="str" cm="1">
+        <f t="array" ref="D43">_xlfn.XLOOKUP(C43,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.XLOOKUP(F43,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
         <v>Maya</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D44" s="2" t="str" cm="1">
+        <f t="array" ref="D44">_xlfn.XLOOKUP(C44,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.XLOOKUP(F44,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
         <v>Mickaël</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D45" s="2" t="str" cm="1">
+        <f t="array" ref="D45">_xlfn.XLOOKUP(C45,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.XLOOKUP(F45,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
         <v>Morgana</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D46" s="2" t="str" cm="1">
+        <f t="array" ref="D46">_xlfn.XLOOKUP(C46,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.XLOOKUP(F46,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
         <v>Morgane</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D47" s="2" t="str" cm="1">
+        <f t="array" ref="D47">_xlfn.XLOOKUP(C47,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.XLOOKUP(F47,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
         <v>Nathalia</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D48" s="2" t="str" cm="1">
+        <f t="array" ref="D48">_xlfn.XLOOKUP(C48,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.XLOOKUP(F48,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
         <v>Noah</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D49" s="2" t="str" cm="1">
+        <f t="array" ref="D49">_xlfn.XLOOKUP(C49,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.XLOOKUP(F49,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
         <v>Patrick</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D50" s="2" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(C50,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(F50,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
         <v>Rama</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D51" s="2" t="str" cm="1">
+        <f t="array" ref="D51">_xlfn.XLOOKUP(C51,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.XLOOKUP(F51,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
         <v>Raphaël</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D52" s="2" t="str" cm="1">
+        <f t="array" ref="D52">_xlfn.XLOOKUP(C52,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.XLOOKUP(F52,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
         <v>Raphaëlle</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D53" s="2" t="str" cm="1">
+        <f t="array" ref="D53">_xlfn.XLOOKUP(C53,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.XLOOKUP(F53,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
         <v>Roxanne</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D54" s="2" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(C54,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(F54,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
         <v>Sébastien</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D55" s="2" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(C55,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(F55,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
         <v>Simon</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D56" s="2" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(C56,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(F56,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
         <v>Theo</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D57" s="2" t="str" cm="1">
+        <f t="array" ref="D57">_xlfn.XLOOKUP(C57,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.XLOOKUP(F57,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
         <v>Thibault</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D58" s="2" t="str" cm="1">
+        <f t="array" ref="D58">_xlfn.XLOOKUP(C58,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.XLOOKUP(F58,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
         <v>Titouan</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D59" s="2" t="str" cm="1">
+        <f t="array" ref="D59">_xlfn.XLOOKUP(C59,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.XLOOKUP(F59,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
         <v>Tristan</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D60" s="2" t="str" cm="1">
+        <f t="array" ref="D60">_xlfn.XLOOKUP(C60,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.XLOOKUP(F60,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
         <v>Yann</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D61" s="2" t="str" cm="1">
+        <f t="array" ref="D61">_xlfn.XLOOKUP(C61,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.XLOOKUP(F61,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
       </c>
+      <c r="D62" s="2" t="str" cm="1">
+        <f t="array" ref="D62">_xlfn.XLOOKUP(C62,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.XLOOKUP(F62,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
+      </c>
+      <c r="D63" s="2" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(C63,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(F63,Table2[Mercredi],Table2[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{691EF265-5902-43C7-85C8-C5547281C515}">
+          <x14:formula1>
+            <xm:f>Concerts!$D$2:$D$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C63 F2:F63</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3903E2BF-703C-4C3A-ACA3-C1A852CBD80C}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2549,518 +4744,1047 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D2" s="2" t="str" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(C2,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="str" cm="1">
+        <f t="array" ref="G2">_xlfn.XLOOKUP(F2,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
         <v>Alegria Lily</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D3" s="2" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.XLOOKUP(C3,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.XLOOKUP(F3,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
         <v>Alexandra</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D4" s="2" t="str" cm="1">
+        <f t="array" ref="D4">_xlfn.XLOOKUP(C4,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.XLOOKUP(F4,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
         <v>Alice</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.XLOOKUP(C5,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.XLOOKUP(F5,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
         <v>Analou</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D6" s="2" t="str" cm="1">
+        <f t="array" ref="D6">_xlfn.XLOOKUP(C6,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.XLOOKUP(F6,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
         <v>Anna</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D7" s="2" t="str" cm="1">
+        <f t="array" ref="D7">_xlfn.XLOOKUP(C7,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.XLOOKUP(F7,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
         <v>Annouk</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D8" s="2" t="str" cm="1">
+        <f t="array" ref="D8">_xlfn.XLOOKUP(C8,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.XLOOKUP(F8,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
         <v>Antonin</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D9" s="2" t="str" cm="1">
+        <f t="array" ref="D9">_xlfn.XLOOKUP(C9,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.XLOOKUP(F9,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
         <v>Arsène</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D10" s="2" t="str" cm="1">
+        <f t="array" ref="D10">_xlfn.XLOOKUP(C10,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.XLOOKUP(F10,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
         <v>Arthur</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D11" s="2" t="str" cm="1">
+        <f t="array" ref="D11">_xlfn.XLOOKUP(C11,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.XLOOKUP(F11,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
         <v>Athénaé</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D12" s="2" t="str" cm="1">
+        <f t="array" ref="D12">_xlfn.XLOOKUP(C12,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.XLOOKUP(F12,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
         <v>Auxence</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D13" s="2" t="str" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(C13,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.XLOOKUP(F13,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
         <v>Ava</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D14" s="2" t="str" cm="1">
+        <f t="array" ref="D14">_xlfn.XLOOKUP(C14,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.XLOOKUP(F14,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
         <v>Benoît</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D15" s="2" t="str" cm="1">
+        <f t="array" ref="D15">_xlfn.XLOOKUP(C15,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.XLOOKUP(F15,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
         <v>Corentin</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D16" s="2" t="str" cm="1">
+        <f t="array" ref="D16">_xlfn.XLOOKUP(C16,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.XLOOKUP(F16,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
         <v>Emma</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D17" s="2" t="str" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(C17,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.XLOOKUP(F17,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
         <v>Enzo</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">_xlfn.XLOOKUP(C18,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.XLOOKUP(F18,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
         <v>Eugénie</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">_xlfn.XLOOKUP(C19,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.XLOOKUP(F19,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
         <v>Iris</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D20" s="2" t="str" cm="1">
+        <f t="array" ref="D20">_xlfn.XLOOKUP(C20,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.XLOOKUP(F20,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
         <v>Jamilah</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D21" s="2" t="str" cm="1">
+        <f t="array" ref="D21">_xlfn.XLOOKUP(C21,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.XLOOKUP(F21,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
         <v>Jolan</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D22" s="2" t="str" cm="1">
+        <f t="array" ref="D22">_xlfn.XLOOKUP(C22,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.XLOOKUP(F22,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
         <v xml:space="preserve">Jonas </v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D23" s="2" t="str" cm="1">
+        <f t="array" ref="D23">_xlfn.XLOOKUP(C23,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str" cm="1">
+        <f t="array" ref="G23">_xlfn.XLOOKUP(F23,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
         <v>Jules</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D24" s="2" t="str" cm="1">
+        <f t="array" ref="D24">_xlfn.XLOOKUP(C24,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.XLOOKUP(F24,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
         <v>Julie</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D25" s="2" t="str" cm="1">
+        <f t="array" ref="D25">_xlfn.XLOOKUP(C25,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.XLOOKUP(F25,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
         <v>Kristel</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D26" s="2" t="str" cm="1">
+        <f t="array" ref="D26">_xlfn.XLOOKUP(C26,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str" cm="1">
+        <f t="array" ref="G26">_xlfn.XLOOKUP(F26,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D27" s="2" t="str" cm="1">
+        <f t="array" ref="D27">_xlfn.XLOOKUP(C27,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.XLOOKUP(F27,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D28" s="2" t="str" cm="1">
+        <f t="array" ref="D28">_xlfn.XLOOKUP(C28,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.XLOOKUP(F28,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
         <v>Lina-Rosa</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D29" s="2" t="str" cm="1">
+        <f t="array" ref="D29">_xlfn.XLOOKUP(C29,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str" cm="1">
+        <f t="array" ref="G29">_xlfn.XLOOKUP(F29,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D30" s="2" t="str" cm="1">
+        <f t="array" ref="D30">_xlfn.XLOOKUP(C30,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str" cm="1">
+        <f t="array" ref="G30">_xlfn.XLOOKUP(F30,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D31" s="2" t="str" cm="1">
+        <f t="array" ref="D31">_xlfn.XLOOKUP(C31,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str" cm="1">
+        <f t="array" ref="G31">_xlfn.XLOOKUP(F31,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D32" s="2" t="str" cm="1">
+        <f t="array" ref="D32">_xlfn.XLOOKUP(C32,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str" cm="1">
+        <f t="array" ref="G32">_xlfn.XLOOKUP(F32,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <v>Post</v>
       </c>
       <c r="B33" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D33" s="2" t="str" cm="1">
+        <f t="array" ref="D33">_xlfn.XLOOKUP(C33,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str" cm="1">
+        <f t="array" ref="G33">_xlfn.XLOOKUP(F33,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
         <v>Louise</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">_xlfn.XLOOKUP(C34,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str" cm="1">
+        <f t="array" ref="G34">_xlfn.XLOOKUP(F34,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
         <v>Lucas</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">_xlfn.XLOOKUP(C35,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str" cm="1">
+        <f t="array" ref="G35">_xlfn.XLOOKUP(F35,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
         <v>Lucie</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D36" s="2" t="str" cm="1">
+        <f t="array" ref="D36">_xlfn.XLOOKUP(C36,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.XLOOKUP(F36,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
         <v>Maëlan</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D37" s="2" t="str" cm="1">
+        <f t="array" ref="D37">_xlfn.XLOOKUP(C37,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str" cm="1">
+        <f t="array" ref="G37">_xlfn.XLOOKUP(F37,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
         <v>Maëlle</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D38" s="2" t="str" cm="1">
+        <f t="array" ref="D38">_xlfn.XLOOKUP(C38,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str" cm="1">
+        <f t="array" ref="G38">_xlfn.XLOOKUP(F38,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
         <v>Marius</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D39" s="2" t="str" cm="1">
+        <f t="array" ref="D39">_xlfn.XLOOKUP(C39,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str" cm="1">
+        <f t="array" ref="G39">_xlfn.XLOOKUP(F39,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
         <v>Marot</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D40" s="2" t="str" cm="1">
+        <f t="array" ref="D40">_xlfn.XLOOKUP(C40,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.XLOOKUP(F40,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
         <v>Mathis</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D41" s="2" t="str" cm="1">
+        <f t="array" ref="D41">_xlfn.XLOOKUP(C41,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.XLOOKUP(F41,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
         <v>Matteo</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D42" s="2" t="str" cm="1">
+        <f t="array" ref="D42">_xlfn.XLOOKUP(C42,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.XLOOKUP(F42,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
         <v>Maxime</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D43" s="2" t="str" cm="1">
+        <f t="array" ref="D43">_xlfn.XLOOKUP(C43,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.XLOOKUP(F43,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
         <v>Maya</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D44" s="2" t="str" cm="1">
+        <f t="array" ref="D44">_xlfn.XLOOKUP(C44,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.XLOOKUP(F44,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
         <v>Mickaël</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D45" s="2" t="str" cm="1">
+        <f t="array" ref="D45">_xlfn.XLOOKUP(C45,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.XLOOKUP(F45,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
         <v>Morgana</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D46" s="2" t="str" cm="1">
+        <f t="array" ref="D46">_xlfn.XLOOKUP(C46,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.XLOOKUP(F46,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
         <v>Morgane</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D47" s="2" t="str" cm="1">
+        <f t="array" ref="D47">_xlfn.XLOOKUP(C47,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.XLOOKUP(F47,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
         <v>Nathalia</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D48" s="2" t="str" cm="1">
+        <f t="array" ref="D48">_xlfn.XLOOKUP(C48,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.XLOOKUP(F48,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
         <v>Noah</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D49" s="2" t="str" cm="1">
+        <f t="array" ref="D49">_xlfn.XLOOKUP(C49,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.XLOOKUP(F49,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
         <v>Patrick</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D50" s="2" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(C50,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(F50,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
         <v>Rama</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D51" s="2" t="str" cm="1">
+        <f t="array" ref="D51">_xlfn.XLOOKUP(C51,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.XLOOKUP(F51,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
         <v>Raphaël</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D52" s="2" t="str" cm="1">
+        <f t="array" ref="D52">_xlfn.XLOOKUP(C52,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.XLOOKUP(F52,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
         <v>Raphaëlle</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D53" s="2" t="str" cm="1">
+        <f t="array" ref="D53">_xlfn.XLOOKUP(C53,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.XLOOKUP(F53,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
         <v>Roxanne</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D54" s="2" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(C54,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(F54,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
         <v>Sébastien</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D55" s="2" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(C55,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(F55,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
         <v>Simon</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D56" s="2" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(C56,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(F56,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
         <v>Theo</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D57" s="2" t="str" cm="1">
+        <f t="array" ref="D57">_xlfn.XLOOKUP(C57,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.XLOOKUP(F57,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
         <v>Thibault</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D58" s="2" t="str" cm="1">
+        <f t="array" ref="D58">_xlfn.XLOOKUP(C58,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.XLOOKUP(F58,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
         <v>Titouan</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D59" s="2" t="str" cm="1">
+        <f t="array" ref="D59">_xlfn.XLOOKUP(C59,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.XLOOKUP(F59,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
         <v>Tristan</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D60" s="2" t="str" cm="1">
+        <f t="array" ref="D60">_xlfn.XLOOKUP(C60,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.XLOOKUP(F60,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
         <v>Yann</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D61" s="2" t="str" cm="1">
+        <f t="array" ref="D61">_xlfn.XLOOKUP(C61,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.XLOOKUP(F61,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
       </c>
+      <c r="D62" s="2" t="str" cm="1">
+        <f t="array" ref="D62">_xlfn.XLOOKUP(C62,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.XLOOKUP(F62,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
+      </c>
+      <c r="D63" s="2" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(C63,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(F63,Table3[Jeudi],Table3[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E36BCB24-C15B-4D97-8AB4-08EAD90B44F4}">
+          <x14:formula1>
+            <xm:f>Concerts!$G$2:$G$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C63 F2:F63</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C361C81-702E-43DD-AD1A-4F9D8DC2CE99}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3068,25 +5792,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <v>Bulka</v>
       </c>
@@ -3094,7 +5827,7 @@
         <v>Alegria Lily</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <v>Bastian</v>
       </c>
@@ -3102,7 +5835,7 @@
         <v>Alexandra</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <v>L'Horset</v>
       </c>
@@ -3110,7 +5843,7 @@
         <v>Alice</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <v>Ledru</v>
       </c>
@@ -3118,7 +5851,7 @@
         <v>Analou</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <v>Mallet</v>
       </c>
@@ -3126,7 +5859,7 @@
         <v>Anna</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <v>Malric</v>
       </c>
@@ -3134,7 +5867,7 @@
         <v>Annouk</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <v>Noël</v>
       </c>
@@ -3142,7 +5875,7 @@
         <v>Antonin</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <v>Tessier</v>
       </c>
@@ -3150,7 +5883,7 @@
         <v>Arsène</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <v>Uldry</v>
       </c>
@@ -3158,7 +5891,7 @@
         <v>Arthur</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <v>Marchand</v>
       </c>
@@ -3166,7 +5899,7 @@
         <v>Athénaé</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <v>Magerand</v>
       </c>
@@ -3174,7 +5907,7 @@
         <v>Auxence</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <v>Baruch</v>
       </c>
@@ -3182,7 +5915,7 @@
         <v>Ava</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <v>Detrain</v>
       </c>
@@ -3190,7 +5923,7 @@
         <v>Benoît</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <v>Meige</v>
       </c>
@@ -3564,6 +6297,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -3573,13 +6314,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A908425B-674F-439F-B8F6-D1D1ECED66A3}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3587,25 +6332,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <v>Bulka</v>
       </c>
@@ -3613,7 +6367,7 @@
         <v>Alegria Lily</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <v>Bastian</v>
       </c>
@@ -3621,7 +6375,7 @@
         <v>Alexandra</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <v>L'Horset</v>
       </c>
@@ -3629,7 +6383,7 @@
         <v>Alice</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <v>Ledru</v>
       </c>
@@ -3637,7 +6391,7 @@
         <v>Analou</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <v>Mallet</v>
       </c>
@@ -3645,7 +6399,7 @@
         <v>Anna</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <v>Malric</v>
       </c>
@@ -3653,7 +6407,7 @@
         <v>Annouk</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <v>Noël</v>
       </c>
@@ -3661,7 +6415,7 @@
         <v>Antonin</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <v>Tessier</v>
       </c>
@@ -3669,7 +6423,7 @@
         <v>Arsène</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <v>Uldry</v>
       </c>
@@ -3677,7 +6431,7 @@
         <v>Arthur</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <v>Marchand</v>
       </c>
@@ -3685,7 +6439,7 @@
         <v>Athénaé</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <v>Magerand</v>
       </c>
@@ -3693,7 +6447,7 @@
         <v>Auxence</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <v>Baruch</v>
       </c>
@@ -3701,7 +6455,7 @@
         <v>Ava</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <v>Detrain</v>
       </c>
@@ -3709,7 +6463,7 @@
         <v>Benoît</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <v>Meige</v>
       </c>
@@ -4083,6 +6837,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -4092,13 +6854,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6875EF01-3F3E-45A7-BC92-0C7AD64098EE}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4106,25 +6872,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <v>Bulka</v>
       </c>
@@ -4132,7 +6907,7 @@
         <v>Alegria Lily</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <v>Bastian</v>
       </c>
@@ -4140,7 +6915,7 @@
         <v>Alexandra</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <v>L'Horset</v>
       </c>
@@ -4148,7 +6923,7 @@
         <v>Alice</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <v>Ledru</v>
       </c>
@@ -4156,7 +6931,7 @@
         <v>Analou</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <v>Mallet</v>
       </c>
@@ -4164,7 +6939,7 @@
         <v>Anna</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <v>Malric</v>
       </c>
@@ -4172,7 +6947,7 @@
         <v>Annouk</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <v>Noël</v>
       </c>
@@ -4180,7 +6955,7 @@
         <v>Antonin</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <v>Tessier</v>
       </c>
@@ -4188,7 +6963,7 @@
         <v>Arsène</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <v>Uldry</v>
       </c>
@@ -4196,7 +6971,7 @@
         <v>Arthur</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <v>Marchand</v>
       </c>
@@ -4204,7 +6979,7 @@
         <v>Athénaé</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <v>Magerand</v>
       </c>
@@ -4212,7 +6987,7 @@
         <v>Auxence</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <v>Baruch</v>
       </c>
@@ -4220,7 +6995,7 @@
         <v>Ava</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <v>Detrain</v>
       </c>
@@ -4228,7 +7003,7 @@
         <v>Benoît</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <v>Meige</v>
       </c>
@@ -4604,7 +7379,1080 @@
         <v>Ysatis</v>
       </c>
     </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163BC770-3B95-40DC-97C2-8529964DDCBE}">
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="3" width="7.921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.69140625" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.23046875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.69140625" customWidth="1"/>
+    <col min="8" max="8" width="7.84375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.23046875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.69140625" customWidth="1"/>
+    <col min="11" max="11" width="7.84375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.23046875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.69140625" customWidth="1"/>
+    <col min="14" max="14" width="7.84375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.23046875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.69140625" customWidth="1"/>
+    <col min="17" max="17" width="7.84375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.23046875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.85763888888888895</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1.0520833333333333</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1.1041666666666665</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="P2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.90625</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.86458333333333326</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="G3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="J3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.84375</v>
+      </c>
+      <c r="M3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0.74652777777777779</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.96875</v>
+      </c>
+      <c r="G4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="J4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.98263888888888895</v>
+      </c>
+      <c r="M4" t="s">
+        <v>112</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1.0451388888888888</v>
+      </c>
+      <c r="P4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0.70486111111111105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.78125</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.92013888888888884</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.96875</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.98263888888888895</v>
+      </c>
+      <c r="M5" t="s">
+        <v>109</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.90277777777777779</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="J6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.77430555555555547</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="P6" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.0590277777777777</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.1041666666666665</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1.0486111111111112</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.98263888888888895</v>
+      </c>
+      <c r="M7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="P7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.85416666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.82291666666666674</v>
+      </c>
+      <c r="J8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="M8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1.0486111111111112</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="P8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.84722222222222221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1.0486111111111112</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1.0486111111111112</v>
+      </c>
+      <c r="P9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="J10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="M10" t="s">
+        <v>110</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.78125</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="P10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.95833333333333326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1.0208333333333333</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.80208333333333326</v>
+      </c>
+      <c r="G11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1.0416666666666667</v>
+      </c>
+      <c r="J11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1.0555555555555556</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1.1076388888888888</v>
+      </c>
+      <c r="M11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.98263888888888895</v>
+      </c>
+      <c r="P11" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0.90277777777777779</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="D12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.0104166666666667</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.0520833333333335</v>
+      </c>
+      <c r="G12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="J12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.0104166666666667</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1.0520833333333335</v>
+      </c>
+      <c r="M12" t="s">
+        <v>111</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.92013888888888884</v>
+      </c>
+      <c r="P12" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>1.0381944444444444</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1.1006944444444444</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="G13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="J13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1.0486111111111112</v>
+      </c>
+      <c r="M13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="P13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.99652777777777779</v>
+      </c>
+      <c r="R13" s="2">
+        <v>1.0381944444444444</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.92708333333333326</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.97569444444444442</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.0590277777777777</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.76736111111111105</v>
+      </c>
+      <c r="J14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M14" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="P14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1.0381944444444444</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.91319444444444453</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.82986111111111116</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.88194444444444453</v>
+      </c>
+      <c r="J15" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.77083333333333326</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="P15" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0.90625</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.85763888888888895</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="J16" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.92708333333333326</v>
+      </c>
+      <c r="M16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="P16" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0.86458333333333326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.0590277777777777</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1.1041666666666665</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="G17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.98263888888888895</v>
+      </c>
+      <c r="J17" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1.0520833333333333</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1.1041666666666665</v>
+      </c>
+      <c r="M17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="P17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="G18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="J18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18" s="2">
+        <v>1.0520833333333333</v>
+      </c>
+      <c r="O18" s="2">
+        <v>1.1041666666666665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.93055555555555547</v>
+      </c>
+      <c r="J19" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="M19" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0.93402777777777779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="6">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/data/blocages.xlsx
+++ b/data/blocages.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DF625E-C03D-4BCC-9EA6-1660955CB301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C761906-A988-4ABE-9FED-23B989B7BA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,12 @@
     <sheet name="Vendredi" sheetId="4" r:id="rId4"/>
     <sheet name="Samedi" sheetId="5" r:id="rId5"/>
     <sheet name="Dimanche" sheetId="6" r:id="rId6"/>
-    <sheet name="Concerts" sheetId="7" r:id="rId7"/>
+    <sheet name="Concerts" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -435,12 +435,48 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -455,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -464,11 +500,80 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -530,6 +635,963 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>652238</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AACFFAD-811D-45C8-9F77-69E185FD94C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6724650" y="184150"/>
+          <a:ext cx="3268438" cy="2946400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" b="1" u="sng" baseline="0"/>
+            <a:t>Blocages</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="0" i="1" u="none" baseline="0"/>
+            <a:t>(liste des voeux)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Choisir les voeux de priorité 1 et 2 pour le mardi.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Les heures du concert s'affichent automatiquement.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Le solveur du planning travaille selon les règles suivantes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>tous les shifts doivent être rempli</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 1 est si possible garantie et complète</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 2 peut être tronquée en partie ou complétement</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>652238</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C5B1C3C-617C-4D73-873D-600CCD1DCFE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6724650" y="184150"/>
+          <a:ext cx="3268438" cy="2940050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" b="1" u="sng" baseline="0"/>
+            <a:t>Blocages</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="0" i="1" u="none" baseline="0"/>
+            <a:t>(liste des voeux)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Choisir les voeux de priorité 1 et 2 pour le mercredi.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Les heures du concert s'affichent automatiquement.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Le solveur du planning travaille selon les règles suivantes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>tous les shifts doivent être rempli</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 1 est si possible garantie et complète</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 2 peut être tronquée en partie ou complétement</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>652238</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C97FF9D-9F09-4594-BC8A-B2A4EB05AB18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6724650" y="184150"/>
+          <a:ext cx="3268438" cy="2959100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" b="1" u="sng" baseline="0"/>
+            <a:t>Blocages</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="0" i="1" u="none" baseline="0"/>
+            <a:t>(liste des voeux)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Choisir les voeux de priorité 1 et 2 pour le jeudi.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Les heures du concert s'affichent automatiquement.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Le solveur du planning travaille selon les règles suivantes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>tous les shifts doivent être rempli</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 1 est si possible garantie et complète</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 2 peut être tronquée en partie ou complétement</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>652238</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD4F98B7-A475-4F22-AF33-F1F72B2E7483}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6724650" y="184150"/>
+          <a:ext cx="3268438" cy="2952750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" b="1" u="sng" baseline="0"/>
+            <a:t>Blocages</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="0" i="1" u="none" baseline="0"/>
+            <a:t>(liste des voeux)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Choisir les voeux de priorité 1 et 2 pour le vendredi.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Les heures du concert s'affichent automatiquement.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Le solveur du planning travaille selon les règles suivantes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>tous les shifts doivent être rempli</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 1 est si possible garantie et complète</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 2 peut être tronquée en partie ou complétement</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>652238</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A46ADDE9-8219-434D-99DA-C3102C600F2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6724650" y="184150"/>
+          <a:ext cx="3268438" cy="2946400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" b="1" u="sng" baseline="0"/>
+            <a:t>Blocages</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="0" i="1" u="none" baseline="0"/>
+            <a:t>(liste des voeux)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Choisir les voeux de priorité 1 et 2 pour le samedi.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Les heures du concert s'affichent automatiquement.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Le solveur du planning travaille selon les règles suivantes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>tous les shifts doivent être rempli</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 1 est si possible garantie et complète</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 2 peut être tronquée en partie ou complétement</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>652238</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B07FFB5A-A427-428B-B77A-A10E7AD6FDEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6724650" y="184150"/>
+          <a:ext cx="3268438" cy="2946400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" b="1" u="sng" baseline="0"/>
+            <a:t>Blocages</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="0" i="1" u="none" baseline="0"/>
+            <a:t>(liste des voeux)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Choisir les voeux de priorité 1 et 2 pour le dimanche.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Les heures du concert s'affichent automatiquement.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>Le solveur du planning travaille selon les règles suivantes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>tous les shifts doivent être rempli</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 1 est si possible garantie et complète</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="628650" lvl="1" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0"/>
+            <a:t>la priorité 2 peut être tronquée en partie ou complétement</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -1572,30 +2634,30 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1609,8 +2671,8 @@
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{8E8B93B6-FFFA-43DA-9F4F-50757F0A0BB7}" name="Mardi"/>
-    <tableColumn id="2" xr3:uid="{C48EDA23-1025-4E75-B10E-227DEE82B8BD}" name="Début" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{B5DF4254-9F45-48A8-ABC0-B6F06CA1B9AB}" name="Fin" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{C48EDA23-1025-4E75-B10E-227DEE82B8BD}" name="Début" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{B5DF4254-9F45-48A8-ABC0-B6F06CA1B9AB}" name="Fin" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1624,8 +2686,8 @@
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{095BD6C4-973C-43C1-80CE-C1A359C07B30}" name="Mercredi"/>
-    <tableColumn id="2" xr3:uid="{94F6012C-3B57-463E-B0C5-19E9BA6495AA}" name="Début" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{4A1A2075-B7E2-42F0-B7D0-601CA6ED90A7}" name="Fin" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{94F6012C-3B57-463E-B0C5-19E9BA6495AA}" name="Début" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{4A1A2075-B7E2-42F0-B7D0-601CA6ED90A7}" name="Fin" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1639,8 +2701,8 @@
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4E6D4E23-2332-4B3F-B79A-9DF4ECB8F9E0}" name="Jeudi"/>
-    <tableColumn id="2" xr3:uid="{99E9964E-444F-45E0-AA5E-D53985498927}" name="Début" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{367FB86A-A425-4FA3-9208-03C03A820C10}" name="Fin" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{99E9964E-444F-45E0-AA5E-D53985498927}" name="Début" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{367FB86A-A425-4FA3-9208-03C03A820C10}" name="Fin" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1654,8 +2716,8 @@
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DE30BCE9-F1AF-4C08-B39E-0C9853F3017D}" name="Vendredi"/>
-    <tableColumn id="2" xr3:uid="{A8DF8A9F-F84C-4960-988E-1E980B175AB2}" name="Début" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{A8243E08-6684-40CA-8875-E3059911D8AA}" name="Fin" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{A8DF8A9F-F84C-4960-988E-1E980B175AB2}" name="Début" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{A8243E08-6684-40CA-8875-E3059911D8AA}" name="Fin" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1669,8 +2731,8 @@
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7A71C11D-7C12-40F2-994A-E8B08FF154F3}" name="Samedi"/>
-    <tableColumn id="2" xr3:uid="{193A2EA8-7572-456D-9AF2-8AB7BDAF4FA2}" name="Début" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{7F3E1EDD-55C8-4CB4-A9F7-92D40BA92403}" name="Fin" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{193A2EA8-7572-456D-9AF2-8AB7BDAF4FA2}" name="Début" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{7F3E1EDD-55C8-4CB4-A9F7-92D40BA92403}" name="Fin" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1684,8 +2746,8 @@
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3F274A3A-E1E0-4299-BDD1-EDE4FB548589}" name="Dimanche"/>
-    <tableColumn id="2" xr3:uid="{79564556-5CF8-4025-B335-FEFC7C6C2FCA}" name="Début" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{1D072B5E-8A60-4C4B-903E-D68DDAC1B33C}" name="Fin" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{79564556-5CF8-4025-B335-FEFC7C6C2FCA}" name="Début" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{1D072B5E-8A60-4C4B-903E-D68DDAC1B33C}" name="Fin" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1976,6 +3038,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1">
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1986,29 +3051,29 @@
     <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2031,14 +3096,14 @@
         <v>1.1041666666666667</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="G2" s="2" cm="1">
         <f t="array" ref="G2:H2">_xlfn.XLOOKUP(F2,Table1[Mardi],Table1[[Début]:[Fin]],"")</f>
-        <v>0.99305555555555558</v>
+        <v>1.0208333333333333</v>
       </c>
       <c r="H2" s="2">
-        <v>5.9027777777777776E-2</v>
+        <v>1.0625</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -3660,7 +4725,18 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F1:F1048576" name="Concerts2"/>
+    <protectedRange sqref="C1:C1048576" name="Concerts1"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3678,6 +4754,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB0BE80-5A54-4435-9512-2BB5720E9EFF}">
+  <sheetPr codeName="Sheet2">
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3688,29 +4767,29 @@
     <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -4708,7 +5787,18 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F1:F1048576" name="Concerts2"/>
+    <protectedRange sqref="C1:C1048576" name="Concerts1"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4726,6 +5816,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3903E2BF-703C-4C3A-ACA3-C1A852CBD80C}">
+  <sheetPr codeName="Sheet3">
+    <tabColor theme="6" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4736,29 +5829,29 @@
     <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5756,7 +6849,18 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F1:F1048576" name="Concerts2"/>
+    <protectedRange sqref="C1:C1048576" name="Concerts1"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -5774,6 +6878,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C361C81-702E-43DD-AD1A-4F9D8DC2CE99}">
+  <sheetPr codeName="Sheet4">
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5784,29 +6891,29 @@
     <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5818,6 +6925,14 @@
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
+      <c r="D2" s="2" t="str" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(C2,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="str" cm="1">
+        <f t="array" ref="G2">_xlfn.XLOOKUP(F2,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
@@ -5826,6 +6941,14 @@
       <c r="B3" t="str">
         <v>Alegria Lily</v>
       </c>
+      <c r="D3" s="2" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.XLOOKUP(C3,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.XLOOKUP(F3,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
@@ -5834,6 +6957,14 @@
       <c r="B4" t="str">
         <v>Alexandra</v>
       </c>
+      <c r="D4" s="2" t="str" cm="1">
+        <f t="array" ref="D4">_xlfn.XLOOKUP(C4,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.XLOOKUP(F4,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
@@ -5842,6 +6973,14 @@
       <c r="B5" t="str">
         <v>Alice</v>
       </c>
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.XLOOKUP(C5,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.XLOOKUP(F5,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
@@ -5850,6 +6989,14 @@
       <c r="B6" t="str">
         <v>Analou</v>
       </c>
+      <c r="D6" s="2" t="str" cm="1">
+        <f t="array" ref="D6">_xlfn.XLOOKUP(C6,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.XLOOKUP(F6,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
@@ -5858,6 +7005,14 @@
       <c r="B7" t="str">
         <v>Anna</v>
       </c>
+      <c r="D7" s="2" t="str" cm="1">
+        <f t="array" ref="D7">_xlfn.XLOOKUP(C7,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.XLOOKUP(F7,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
@@ -5866,6 +7021,14 @@
       <c r="B8" t="str">
         <v>Annouk</v>
       </c>
+      <c r="D8" s="2" t="str" cm="1">
+        <f t="array" ref="D8">_xlfn.XLOOKUP(C8,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.XLOOKUP(F8,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
@@ -5874,6 +7037,14 @@
       <c r="B9" t="str">
         <v>Antonin</v>
       </c>
+      <c r="D9" s="2" t="str" cm="1">
+        <f t="array" ref="D9">_xlfn.XLOOKUP(C9,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.XLOOKUP(F9,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
@@ -5882,6 +7053,14 @@
       <c r="B10" t="str">
         <v>Arsène</v>
       </c>
+      <c r="D10" s="2" t="str" cm="1">
+        <f t="array" ref="D10">_xlfn.XLOOKUP(C10,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.XLOOKUP(F10,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
@@ -5890,6 +7069,14 @@
       <c r="B11" t="str">
         <v>Arthur</v>
       </c>
+      <c r="D11" s="2" t="str" cm="1">
+        <f t="array" ref="D11">_xlfn.XLOOKUP(C11,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.XLOOKUP(F11,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
@@ -5898,6 +7085,14 @@
       <c r="B12" t="str">
         <v>Athénaé</v>
       </c>
+      <c r="D12" s="2" t="str" cm="1">
+        <f t="array" ref="D12">_xlfn.XLOOKUP(C12,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.XLOOKUP(F12,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
@@ -5906,6 +7101,14 @@
       <c r="B13" t="str">
         <v>Auxence</v>
       </c>
+      <c r="D13" s="2" t="str" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(C13,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.XLOOKUP(F13,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
@@ -5914,6 +7117,14 @@
       <c r="B14" t="str">
         <v>Ava</v>
       </c>
+      <c r="D14" s="2" t="str" cm="1">
+        <f t="array" ref="D14">_xlfn.XLOOKUP(C14,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.XLOOKUP(F14,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
@@ -5922,6 +7133,14 @@
       <c r="B15" t="str">
         <v>Benoît</v>
       </c>
+      <c r="D15" s="2" t="str" cm="1">
+        <f t="array" ref="D15">_xlfn.XLOOKUP(C15,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.XLOOKUP(F15,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
@@ -5930,390 +7149,1872 @@
       <c r="B16" t="str">
         <v>Corentin</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D16" s="2" t="str" cm="1">
+        <f t="array" ref="D16">_xlfn.XLOOKUP(C16,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.XLOOKUP(F16,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
         <v>Emma</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D17" s="2" t="str" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(C17,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.XLOOKUP(F17,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
         <v>Enzo</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">_xlfn.XLOOKUP(C18,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.XLOOKUP(F18,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
         <v>Eugénie</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">_xlfn.XLOOKUP(C19,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.XLOOKUP(F19,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
         <v>Iris</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D20" s="2" t="str" cm="1">
+        <f t="array" ref="D20">_xlfn.XLOOKUP(C20,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.XLOOKUP(F20,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
         <v>Jamilah</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D21" s="2" t="str" cm="1">
+        <f t="array" ref="D21">_xlfn.XLOOKUP(C21,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.XLOOKUP(F21,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
         <v>Jolan</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D22" s="2" t="str" cm="1">
+        <f t="array" ref="D22">_xlfn.XLOOKUP(C22,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.XLOOKUP(F22,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
         <v xml:space="preserve">Jonas </v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D23" s="2" t="str" cm="1">
+        <f t="array" ref="D23">_xlfn.XLOOKUP(C23,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str" cm="1">
+        <f t="array" ref="G23">_xlfn.XLOOKUP(F23,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
         <v>Jules</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D24" s="2" t="str" cm="1">
+        <f t="array" ref="D24">_xlfn.XLOOKUP(C24,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.XLOOKUP(F24,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
         <v>Julie</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D25" s="2" t="str" cm="1">
+        <f t="array" ref="D25">_xlfn.XLOOKUP(C25,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.XLOOKUP(F25,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
         <v>Kristel</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D26" s="2" t="str" cm="1">
+        <f t="array" ref="D26">_xlfn.XLOOKUP(C26,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str" cm="1">
+        <f t="array" ref="G26">_xlfn.XLOOKUP(F26,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D27" s="2" t="str" cm="1">
+        <f t="array" ref="D27">_xlfn.XLOOKUP(C27,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.XLOOKUP(F27,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D28" s="2" t="str" cm="1">
+        <f t="array" ref="D28">_xlfn.XLOOKUP(C28,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.XLOOKUP(F28,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
         <v>Lina-Rosa</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D29" s="2" t="str" cm="1">
+        <f t="array" ref="D29">_xlfn.XLOOKUP(C29,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str" cm="1">
+        <f t="array" ref="G29">_xlfn.XLOOKUP(F29,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D30" s="2" t="str" cm="1">
+        <f t="array" ref="D30">_xlfn.XLOOKUP(C30,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str" cm="1">
+        <f t="array" ref="G30">_xlfn.XLOOKUP(F30,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D31" s="2" t="str" cm="1">
+        <f t="array" ref="D31">_xlfn.XLOOKUP(C31,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str" cm="1">
+        <f t="array" ref="G31">_xlfn.XLOOKUP(F31,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D32" s="2" t="str" cm="1">
+        <f t="array" ref="D32">_xlfn.XLOOKUP(C32,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str" cm="1">
+        <f t="array" ref="G32">_xlfn.XLOOKUP(F32,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <v>Post</v>
       </c>
       <c r="B33" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D33" s="2" t="str" cm="1">
+        <f t="array" ref="D33">_xlfn.XLOOKUP(C33,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str" cm="1">
+        <f t="array" ref="G33">_xlfn.XLOOKUP(F33,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
         <v>Louise</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">_xlfn.XLOOKUP(C34,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str" cm="1">
+        <f t="array" ref="G34">_xlfn.XLOOKUP(F34,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
         <v>Lucas</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">_xlfn.XLOOKUP(C35,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str" cm="1">
+        <f t="array" ref="G35">_xlfn.XLOOKUP(F35,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
         <v>Lucie</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D36" s="2" t="str" cm="1">
+        <f t="array" ref="D36">_xlfn.XLOOKUP(C36,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.XLOOKUP(F36,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
         <v>Maëlan</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D37" s="2" t="str" cm="1">
+        <f t="array" ref="D37">_xlfn.XLOOKUP(C37,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str" cm="1">
+        <f t="array" ref="G37">_xlfn.XLOOKUP(F37,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
         <v>Maëlle</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D38" s="2" t="str" cm="1">
+        <f t="array" ref="D38">_xlfn.XLOOKUP(C38,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str" cm="1">
+        <f t="array" ref="G38">_xlfn.XLOOKUP(F38,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
         <v>Marius</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D39" s="2" t="str" cm="1">
+        <f t="array" ref="D39">_xlfn.XLOOKUP(C39,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str" cm="1">
+        <f t="array" ref="G39">_xlfn.XLOOKUP(F39,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
         <v>Marot</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D40" s="2" t="str" cm="1">
+        <f t="array" ref="D40">_xlfn.XLOOKUP(C40,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.XLOOKUP(F40,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
         <v>Mathis</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D41" s="2" t="str" cm="1">
+        <f t="array" ref="D41">_xlfn.XLOOKUP(C41,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.XLOOKUP(F41,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
         <v>Matteo</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D42" s="2" t="str" cm="1">
+        <f t="array" ref="D42">_xlfn.XLOOKUP(C42,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.XLOOKUP(F42,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
         <v>Maxime</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D43" s="2" t="str" cm="1">
+        <f t="array" ref="D43">_xlfn.XLOOKUP(C43,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.XLOOKUP(F43,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
         <v>Maya</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D44" s="2" t="str" cm="1">
+        <f t="array" ref="D44">_xlfn.XLOOKUP(C44,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.XLOOKUP(F44,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
         <v>Mickaël</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D45" s="2" t="str" cm="1">
+        <f t="array" ref="D45">_xlfn.XLOOKUP(C45,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.XLOOKUP(F45,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
         <v>Morgana</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D46" s="2" t="str" cm="1">
+        <f t="array" ref="D46">_xlfn.XLOOKUP(C46,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.XLOOKUP(F46,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
         <v>Morgane</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D47" s="2" t="str" cm="1">
+        <f t="array" ref="D47">_xlfn.XLOOKUP(C47,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.XLOOKUP(F47,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
         <v>Nathalia</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D48" s="2" t="str" cm="1">
+        <f t="array" ref="D48">_xlfn.XLOOKUP(C48,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.XLOOKUP(F48,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
         <v>Noah</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D49" s="2" t="str" cm="1">
+        <f t="array" ref="D49">_xlfn.XLOOKUP(C49,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.XLOOKUP(F49,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
         <v>Patrick</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D50" s="2" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(C50,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(F50,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
         <v>Rama</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D51" s="2" t="str" cm="1">
+        <f t="array" ref="D51">_xlfn.XLOOKUP(C51,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.XLOOKUP(F51,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
         <v>Raphaël</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D52" s="2" t="str" cm="1">
+        <f t="array" ref="D52">_xlfn.XLOOKUP(C52,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.XLOOKUP(F52,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
         <v>Raphaëlle</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D53" s="2" t="str" cm="1">
+        <f t="array" ref="D53">_xlfn.XLOOKUP(C53,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.XLOOKUP(F53,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
         <v>Roxanne</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D54" s="2" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(C54,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(F54,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
         <v>Sébastien</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D55" s="2" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(C55,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(F55,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
         <v>Simon</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D56" s="2" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(C56,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(F56,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
         <v>Theo</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D57" s="2" t="str" cm="1">
+        <f t="array" ref="D57">_xlfn.XLOOKUP(C57,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.XLOOKUP(F57,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
         <v>Thibault</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D58" s="2" t="str" cm="1">
+        <f t="array" ref="D58">_xlfn.XLOOKUP(C58,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.XLOOKUP(F58,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
         <v>Titouan</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D59" s="2" t="str" cm="1">
+        <f t="array" ref="D59">_xlfn.XLOOKUP(C59,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.XLOOKUP(F59,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
         <v>Tristan</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D60" s="2" t="str" cm="1">
+        <f t="array" ref="D60">_xlfn.XLOOKUP(C60,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.XLOOKUP(F60,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
         <v>Yann</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D61" s="2" t="str" cm="1">
+        <f t="array" ref="D61">_xlfn.XLOOKUP(C61,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.XLOOKUP(F61,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D62" s="2" t="str" cm="1">
+        <f t="array" ref="D62">_xlfn.XLOOKUP(C62,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.XLOOKUP(F62,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
         <v>Mireille</v>
       </c>
+      <c r="D63" s="2" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(C63,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(F63,Table4[Vendredi],Table4[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F1:F1048576" name="Concerts2"/>
+    <protectedRange sqref="C1:C1048576" name="Concerts1"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7CDA9E57-753E-443D-9CAA-23D21A46F9BB}">
+          <x14:formula1>
+            <xm:f>Concerts!$J$2:$J$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C63 F2:F63</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A908425B-674F-439F-B8F6-D1D1ECED66A3}">
+  <sheetPr codeName="Sheet5">
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="13.765625" customWidth="1"/>
+    <col min="3" max="3" width="11.53515625" customWidth="1"/>
+    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.53515625" customWidth="1"/>
+    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <v>Bouvet</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Agathe</v>
+      </c>
+      <c r="D2" s="2" t="str" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(C2,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="str" cm="1">
+        <f t="array" ref="G2">_xlfn.XLOOKUP(F2,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="str">
+        <v>Bulka</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Alegria Lily</v>
+      </c>
+      <c r="D3" s="2" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.XLOOKUP(C3,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.XLOOKUP(F3,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" t="str">
+        <v>Bastian</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Alexandra</v>
+      </c>
+      <c r="D4" s="2" t="str" cm="1">
+        <f t="array" ref="D4">_xlfn.XLOOKUP(C4,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.XLOOKUP(F4,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" t="str">
+        <v>L'Horset</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Alice</v>
+      </c>
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.XLOOKUP(C5,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.XLOOKUP(F5,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="str">
+        <v>Ledru</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Analou</v>
+      </c>
+      <c r="D6" s="2" t="str" cm="1">
+        <f t="array" ref="D6">_xlfn.XLOOKUP(C6,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.XLOOKUP(F6,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="str">
+        <v>Mallet</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Anna</v>
+      </c>
+      <c r="D7" s="2" t="str" cm="1">
+        <f t="array" ref="D7">_xlfn.XLOOKUP(C7,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.XLOOKUP(F7,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="str">
+        <v>Malric</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Annouk</v>
+      </c>
+      <c r="D8" s="2" t="str" cm="1">
+        <f t="array" ref="D8">_xlfn.XLOOKUP(C8,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.XLOOKUP(F8,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="str">
+        <v>Noël</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="D9" s="2" t="str" cm="1">
+        <f t="array" ref="D9">_xlfn.XLOOKUP(C9,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.XLOOKUP(F9,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="str">
+        <v>Tessier</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Arsène</v>
+      </c>
+      <c r="D10" s="2" t="str" cm="1">
+        <f t="array" ref="D10">_xlfn.XLOOKUP(C10,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.XLOOKUP(F10,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="str">
+        <v>Uldry</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Arthur</v>
+      </c>
+      <c r="D11" s="2" t="str" cm="1">
+        <f t="array" ref="D11">_xlfn.XLOOKUP(C11,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.XLOOKUP(F11,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="str">
+        <v>Marchand</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Athénaé</v>
+      </c>
+      <c r="D12" s="2" t="str" cm="1">
+        <f t="array" ref="D12">_xlfn.XLOOKUP(C12,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.XLOOKUP(F12,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="str">
+        <v>Magerand</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Auxence</v>
+      </c>
+      <c r="D13" s="2" t="str" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(C13,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.XLOOKUP(F13,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="str">
+        <v>Baruch</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Ava</v>
+      </c>
+      <c r="D14" s="2" t="str" cm="1">
+        <f t="array" ref="D14">_xlfn.XLOOKUP(C14,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.XLOOKUP(F14,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="str">
+        <v>Detrain</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Benoît</v>
+      </c>
+      <c r="D15" s="2" t="str" cm="1">
+        <f t="array" ref="D15">_xlfn.XLOOKUP(C15,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.XLOOKUP(F15,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="str">
+        <v>Meige</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Corentin</v>
+      </c>
+      <c r="D16" s="2" t="str" cm="1">
+        <f t="array" ref="D16">_xlfn.XLOOKUP(C16,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.XLOOKUP(F16,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" t="str">
+        <v>De Filippo</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Emma</v>
+      </c>
+      <c r="D17" s="2" t="str" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(C17,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.XLOOKUP(F17,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" t="str">
+        <v>Maître</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Enzo</v>
+      </c>
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">_xlfn.XLOOKUP(C18,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.XLOOKUP(F18,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" t="str">
+        <v>Prouvost</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Eugénie</v>
+      </c>
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">_xlfn.XLOOKUP(C19,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.XLOOKUP(F19,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" t="str">
+        <v xml:space="preserve">Rakotonandrasana </v>
+      </c>
+      <c r="B20" t="str">
+        <v>Iris</v>
+      </c>
+      <c r="D20" s="2" t="str" cm="1">
+        <f t="array" ref="D20">_xlfn.XLOOKUP(C20,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.XLOOKUP(F20,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" t="str">
+        <v>Bürgisser</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Jamilah</v>
+      </c>
+      <c r="D21" s="2" t="str" cm="1">
+        <f t="array" ref="D21">_xlfn.XLOOKUP(C21,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.XLOOKUP(F21,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" t="str">
+        <v>Ruscio</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Jolan</v>
+      </c>
+      <c r="D22" s="2" t="str" cm="1">
+        <f t="array" ref="D22">_xlfn.XLOOKUP(C22,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.XLOOKUP(F22,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" t="str">
+        <v>Wuilloud</v>
+      </c>
+      <c r="B23" t="str">
+        <v xml:space="preserve">Jonas </v>
+      </c>
+      <c r="D23" s="2" t="str" cm="1">
+        <f t="array" ref="D23">_xlfn.XLOOKUP(C23,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str" cm="1">
+        <f t="array" ref="G23">_xlfn.XLOOKUP(F23,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" t="str">
+        <v>Pirolley</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Jules</v>
+      </c>
+      <c r="D24" s="2" t="str" cm="1">
+        <f t="array" ref="D24">_xlfn.XLOOKUP(C24,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.XLOOKUP(F24,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" t="str">
+        <v>Chavaillaz</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Julie</v>
+      </c>
+      <c r="D25" s="2" t="str" cm="1">
+        <f t="array" ref="D25">_xlfn.XLOOKUP(C25,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.XLOOKUP(F25,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" t="str">
+        <v>Oeschger</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Kristel</v>
+      </c>
+      <c r="D26" s="2" t="str" cm="1">
+        <f t="array" ref="D26">_xlfn.XLOOKUP(C26,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str" cm="1">
+        <f t="array" ref="G26">_xlfn.XLOOKUP(F26,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" t="str">
+        <v>Baltzinger</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Léa</v>
+      </c>
+      <c r="D27" s="2" t="str" cm="1">
+        <f t="array" ref="D27">_xlfn.XLOOKUP(C27,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.XLOOKUP(F27,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" t="str">
+        <v>Chambaz</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Léa</v>
+      </c>
+      <c r="D28" s="2" t="str" cm="1">
+        <f t="array" ref="D28">_xlfn.XLOOKUP(C28,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.XLOOKUP(F28,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" t="str">
+        <v>Ledru</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Lina-Rosa</v>
+      </c>
+      <c r="D29" s="2" t="str" cm="1">
+        <f t="array" ref="D29">_xlfn.XLOOKUP(C29,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str" cm="1">
+        <f t="array" ref="G29">_xlfn.XLOOKUP(F29,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" t="str">
+        <v>Jaquet</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Lisa</v>
+      </c>
+      <c r="D30" s="2" t="str" cm="1">
+        <f t="array" ref="D30">_xlfn.XLOOKUP(C30,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str" cm="1">
+        <f t="array" ref="G30">_xlfn.XLOOKUP(F30,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" t="str">
+        <v>Magnin</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Lisa</v>
+      </c>
+      <c r="D31" s="2" t="str" cm="1">
+        <f t="array" ref="D31">_xlfn.XLOOKUP(C31,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str" cm="1">
+        <f t="array" ref="G31">_xlfn.XLOOKUP(F31,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" t="str">
+        <v>Cardis</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Louis</v>
+      </c>
+      <c r="D32" s="2" t="str" cm="1">
+        <f t="array" ref="D32">_xlfn.XLOOKUP(C32,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str" cm="1">
+        <f t="array" ref="G32">_xlfn.XLOOKUP(F32,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" t="str">
+        <v>Post</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Louis</v>
+      </c>
+      <c r="D33" s="2" t="str" cm="1">
+        <f t="array" ref="D33">_xlfn.XLOOKUP(C33,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str" cm="1">
+        <f t="array" ref="G33">_xlfn.XLOOKUP(F33,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" t="str">
+        <v>Blanchard</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Louise</v>
+      </c>
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">_xlfn.XLOOKUP(C34,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str" cm="1">
+        <f t="array" ref="G34">_xlfn.XLOOKUP(F34,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" t="str">
+        <v>Chastroux</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Lucas</v>
+      </c>
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">_xlfn.XLOOKUP(C35,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str" cm="1">
+        <f t="array" ref="G35">_xlfn.XLOOKUP(F35,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" t="str">
+        <v>Meyer</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Lucie</v>
+      </c>
+      <c r="D36" s="2" t="str" cm="1">
+        <f t="array" ref="D36">_xlfn.XLOOKUP(C36,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.XLOOKUP(F36,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" t="str">
+        <v>Ménétrey</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Maëlan</v>
+      </c>
+      <c r="D37" s="2" t="str" cm="1">
+        <f t="array" ref="D37">_xlfn.XLOOKUP(C37,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str" cm="1">
+        <f t="array" ref="G37">_xlfn.XLOOKUP(F37,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" t="str">
+        <v>Chambaz</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Maëlle</v>
+      </c>
+      <c r="D38" s="2" t="str" cm="1">
+        <f t="array" ref="D38">_xlfn.XLOOKUP(C38,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str" cm="1">
+        <f t="array" ref="G38">_xlfn.XLOOKUP(F38,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" t="str">
+        <v>Felix</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Marius</v>
+      </c>
+      <c r="D39" s="2" t="str" cm="1">
+        <f t="array" ref="D39">_xlfn.XLOOKUP(C39,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str" cm="1">
+        <f t="array" ref="G39">_xlfn.XLOOKUP(F39,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" t="str">
+        <v>Ledru</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Marot</v>
+      </c>
+      <c r="D40" s="2" t="str" cm="1">
+        <f t="array" ref="D40">_xlfn.XLOOKUP(C40,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.XLOOKUP(F40,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" t="str">
+        <v>Cuinet</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Mathis</v>
+      </c>
+      <c r="D41" s="2" t="str" cm="1">
+        <f t="array" ref="D41">_xlfn.XLOOKUP(C41,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.XLOOKUP(F41,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" t="str">
+        <v>Gavin</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Matteo</v>
+      </c>
+      <c r="D42" s="2" t="str" cm="1">
+        <f t="array" ref="D42">_xlfn.XLOOKUP(C42,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.XLOOKUP(F42,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" t="str">
+        <v>Debray</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Maxime</v>
+      </c>
+      <c r="D43" s="2" t="str" cm="1">
+        <f t="array" ref="D43">_xlfn.XLOOKUP(C43,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.XLOOKUP(F43,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" t="str">
+        <v>Corbelli</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Maya</v>
+      </c>
+      <c r="D44" s="2" t="str" cm="1">
+        <f t="array" ref="D44">_xlfn.XLOOKUP(C44,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.XLOOKUP(F44,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" t="str">
+        <v>Pasche</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Mickaël</v>
+      </c>
+      <c r="D45" s="2" t="str" cm="1">
+        <f t="array" ref="D45">_xlfn.XLOOKUP(C45,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.XLOOKUP(F45,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" t="str">
+        <v>Fargues</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Morgana</v>
+      </c>
+      <c r="D46" s="2" t="str" cm="1">
+        <f t="array" ref="D46">_xlfn.XLOOKUP(C46,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.XLOOKUP(F46,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" t="str">
+        <v>Scyboz (Lambelet)</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Morgane</v>
+      </c>
+      <c r="D47" s="2" t="str" cm="1">
+        <f t="array" ref="D47">_xlfn.XLOOKUP(C47,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.XLOOKUP(F47,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" t="str">
+        <v>Koux</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Nathalia</v>
+      </c>
+      <c r="D48" s="2" t="str" cm="1">
+        <f t="array" ref="D48">_xlfn.XLOOKUP(C48,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.XLOOKUP(F48,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" t="str">
+        <v>Cherpillod</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Noah</v>
+      </c>
+      <c r="D49" s="2" t="str" cm="1">
+        <f t="array" ref="D49">_xlfn.XLOOKUP(C49,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.XLOOKUP(F49,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" t="str">
+        <v>Chambaz</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Patrick</v>
+      </c>
+      <c r="D50" s="2" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(C50,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(F50,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" t="str">
+        <v>Assaoui</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Rama</v>
+      </c>
+      <c r="D51" s="2" t="str" cm="1">
+        <f t="array" ref="D51">_xlfn.XLOOKUP(C51,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.XLOOKUP(F51,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" t="str">
+        <v>Lacroze</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Raphaël</v>
+      </c>
+      <c r="D52" s="2" t="str" cm="1">
+        <f t="array" ref="D52">_xlfn.XLOOKUP(C52,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.XLOOKUP(F52,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" t="str">
+        <v>Neidhart</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Raphaëlle</v>
+      </c>
+      <c r="D53" s="2" t="str" cm="1">
+        <f t="array" ref="D53">_xlfn.XLOOKUP(C53,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.XLOOKUP(F53,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" t="str">
+        <v xml:space="preserve">Lanni </v>
+      </c>
+      <c r="B54" t="str">
+        <v>Roxanne</v>
+      </c>
+      <c r="D54" s="2" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(C54,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(F54,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" t="str">
+        <v>Schiesser</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Sébastien</v>
+      </c>
+      <c r="D55" s="2" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(C55,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(F55,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" t="str">
+        <v>Lambelet</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Simon</v>
+      </c>
+      <c r="D56" s="2" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(C56,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(F56,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" t="str">
+        <v>Cyprien</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Theo</v>
+      </c>
+      <c r="D57" s="2" t="str" cm="1">
+        <f t="array" ref="D57">_xlfn.XLOOKUP(C57,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.XLOOKUP(F57,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" t="str">
+        <v>Clerici</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Thibault</v>
+      </c>
+      <c r="D58" s="2" t="str" cm="1">
+        <f t="array" ref="D58">_xlfn.XLOOKUP(C58,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.XLOOKUP(F58,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" t="str">
+        <v>Ménétrey</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Titouan</v>
+      </c>
+      <c r="D59" s="2" t="str" cm="1">
+        <f t="array" ref="D59">_xlfn.XLOOKUP(C59,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.XLOOKUP(F59,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60" t="str">
+        <v>Clerici</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Tristan</v>
+      </c>
+      <c r="D60" s="2" t="str" cm="1">
+        <f t="array" ref="D60">_xlfn.XLOOKUP(C60,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.XLOOKUP(F60,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" t="str">
+        <v>Bally</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Yann</v>
+      </c>
+      <c r="D61" s="2" t="str" cm="1">
+        <f t="array" ref="D61">_xlfn.XLOOKUP(C61,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.XLOOKUP(F61,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" t="str">
+        <v>Ménétrey</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Ysatis</v>
+      </c>
+      <c r="D62" s="2" t="str" cm="1">
+        <f t="array" ref="D62">_xlfn.XLOOKUP(C62,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.XLOOKUP(F62,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
+      </c>
+      <c r="D63" s="2" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(C63,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(F63,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="D64" s="2" t="str" cm="1">
+        <f t="array" ref="D64">_xlfn.XLOOKUP(C64,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str" cm="1">
+        <f t="array" ref="G64">_xlfn.XLOOKUP(F64,Table5[Samedi],Table5[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F1:F1048576" name="Concerts2"/>
+    <protectedRange sqref="C1:C1048576" name="Concerts1"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{449F78A8-1F5E-4E5B-A0FE-59785D5AB99A}">
+          <x14:formula1>
+            <xm:f>Concerts!$M$2:$M$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C64 F2:F64</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6875EF01-3F3E-45A7-BC92-0C7AD64098EE}">
+  <sheetPr codeName="Sheet6">
+    <tabColor theme="2" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6324,29 +9025,29 @@
     <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="15" t="s">
         <v>3</v>
       </c>
     </row>
@@ -6358,6 +9059,14 @@
       <c r="B2" t="str">
         <v>Agathe</v>
       </c>
+      <c r="D2" s="2" t="str" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(C2,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="str" cm="1">
+        <f t="array" ref="G2">_xlfn.XLOOKUP(F2,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
@@ -6366,6 +9075,14 @@
       <c r="B3" t="str">
         <v>Alegria Lily</v>
       </c>
+      <c r="D3" s="2" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.XLOOKUP(C3,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.XLOOKUP(F3,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
@@ -6374,6 +9091,14 @@
       <c r="B4" t="str">
         <v>Alexandra</v>
       </c>
+      <c r="D4" s="2" t="str" cm="1">
+        <f t="array" ref="D4">_xlfn.XLOOKUP(C4,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.XLOOKUP(F4,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
@@ -6382,6 +9107,14 @@
       <c r="B5" t="str">
         <v>Alice</v>
       </c>
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.XLOOKUP(C5,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.XLOOKUP(F5,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
@@ -6390,6 +9123,14 @@
       <c r="B6" t="str">
         <v>Analou</v>
       </c>
+      <c r="D6" s="2" t="str" cm="1">
+        <f t="array" ref="D6">_xlfn.XLOOKUP(C6,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.XLOOKUP(F6,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
@@ -6398,6 +9139,14 @@
       <c r="B7" t="str">
         <v>Anna</v>
       </c>
+      <c r="D7" s="2" t="str" cm="1">
+        <f t="array" ref="D7">_xlfn.XLOOKUP(C7,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.XLOOKUP(F7,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
@@ -6406,6 +9155,14 @@
       <c r="B8" t="str">
         <v>Annouk</v>
       </c>
+      <c r="D8" s="2" t="str" cm="1">
+        <f t="array" ref="D8">_xlfn.XLOOKUP(C8,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.XLOOKUP(F8,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
@@ -6414,6 +9171,14 @@
       <c r="B9" t="str">
         <v>Antonin</v>
       </c>
+      <c r="D9" s="2" t="str" cm="1">
+        <f t="array" ref="D9">_xlfn.XLOOKUP(C9,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.XLOOKUP(F9,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
@@ -6422,6 +9187,14 @@
       <c r="B10" t="str">
         <v>Arsène</v>
       </c>
+      <c r="D10" s="2" t="str" cm="1">
+        <f t="array" ref="D10">_xlfn.XLOOKUP(C10,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.XLOOKUP(F10,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
@@ -6430,6 +9203,14 @@
       <c r="B11" t="str">
         <v>Arthur</v>
       </c>
+      <c r="D11" s="2" t="str" cm="1">
+        <f t="array" ref="D11">_xlfn.XLOOKUP(C11,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.XLOOKUP(F11,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
@@ -6438,6 +9219,14 @@
       <c r="B12" t="str">
         <v>Athénaé</v>
       </c>
+      <c r="D12" s="2" t="str" cm="1">
+        <f t="array" ref="D12">_xlfn.XLOOKUP(C12,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.XLOOKUP(F12,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
@@ -6446,6 +9235,14 @@
       <c r="B13" t="str">
         <v>Auxence</v>
       </c>
+      <c r="D13" s="2" t="str" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(C13,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.XLOOKUP(F13,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
@@ -6454,6 +9251,14 @@
       <c r="B14" t="str">
         <v>Ava</v>
       </c>
+      <c r="D14" s="2" t="str" cm="1">
+        <f t="array" ref="D14">_xlfn.XLOOKUP(C14,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.XLOOKUP(F14,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
@@ -6462,6 +9267,14 @@
       <c r="B15" t="str">
         <v>Benoît</v>
       </c>
+      <c r="D15" s="2" t="str" cm="1">
+        <f t="array" ref="D15">_xlfn.XLOOKUP(C15,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.XLOOKUP(F15,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
@@ -6470,930 +9283,798 @@
       <c r="B16" t="str">
         <v>Corentin</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D16" s="2" t="str" cm="1">
+        <f t="array" ref="D16">_xlfn.XLOOKUP(C16,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.XLOOKUP(F16,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
         <v>Emma</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D17" s="2" t="str" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(C17,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.XLOOKUP(F17,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
         <v>Enzo</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">_xlfn.XLOOKUP(C18,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.XLOOKUP(F18,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
         <v>Eugénie</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">_xlfn.XLOOKUP(C19,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.XLOOKUP(F19,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
         <v>Iris</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D20" s="2" t="str" cm="1">
+        <f t="array" ref="D20">_xlfn.XLOOKUP(C20,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.XLOOKUP(F20,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
         <v>Jamilah</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D21" s="2" t="str" cm="1">
+        <f t="array" ref="D21">_xlfn.XLOOKUP(C21,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.XLOOKUP(F21,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
         <v>Jolan</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D22" s="2" t="str" cm="1">
+        <f t="array" ref="D22">_xlfn.XLOOKUP(C22,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.XLOOKUP(F22,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
         <v xml:space="preserve">Jonas </v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D23" s="2" t="str" cm="1">
+        <f t="array" ref="D23">_xlfn.XLOOKUP(C23,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str" cm="1">
+        <f t="array" ref="G23">_xlfn.XLOOKUP(F23,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
         <v>Jules</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D24" s="2" t="str" cm="1">
+        <f t="array" ref="D24">_xlfn.XLOOKUP(C24,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.XLOOKUP(F24,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
         <v>Julie</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D25" s="2" t="str" cm="1">
+        <f t="array" ref="D25">_xlfn.XLOOKUP(C25,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.XLOOKUP(F25,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
         <v>Kristel</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D26" s="2" t="str" cm="1">
+        <f t="array" ref="D26">_xlfn.XLOOKUP(C26,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str" cm="1">
+        <f t="array" ref="G26">_xlfn.XLOOKUP(F26,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D27" s="2" t="str" cm="1">
+        <f t="array" ref="D27">_xlfn.XLOOKUP(C27,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.XLOOKUP(F27,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
         <v>Léa</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D28" s="2" t="str" cm="1">
+        <f t="array" ref="D28">_xlfn.XLOOKUP(C28,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.XLOOKUP(F28,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
         <v>Lina-Rosa</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D29" s="2" t="str" cm="1">
+        <f t="array" ref="D29">_xlfn.XLOOKUP(C29,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str" cm="1">
+        <f t="array" ref="G29">_xlfn.XLOOKUP(F29,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D30" s="2" t="str" cm="1">
+        <f t="array" ref="D30">_xlfn.XLOOKUP(C30,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str" cm="1">
+        <f t="array" ref="G30">_xlfn.XLOOKUP(F30,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
         <v>Lisa</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D31" s="2" t="str" cm="1">
+        <f t="array" ref="D31">_xlfn.XLOOKUP(C31,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str" cm="1">
+        <f t="array" ref="G31">_xlfn.XLOOKUP(F31,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D32" s="2" t="str" cm="1">
+        <f t="array" ref="D32">_xlfn.XLOOKUP(C32,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str" cm="1">
+        <f t="array" ref="G32">_xlfn.XLOOKUP(F32,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <v>Post</v>
       </c>
       <c r="B33" t="str">
         <v>Louis</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D33" s="2" t="str" cm="1">
+        <f t="array" ref="D33">_xlfn.XLOOKUP(C33,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str" cm="1">
+        <f t="array" ref="G33">_xlfn.XLOOKUP(F33,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
         <v>Louise</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">_xlfn.XLOOKUP(C34,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str" cm="1">
+        <f t="array" ref="G34">_xlfn.XLOOKUP(F34,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
         <v>Lucas</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">_xlfn.XLOOKUP(C35,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str" cm="1">
+        <f t="array" ref="G35">_xlfn.XLOOKUP(F35,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
         <v>Lucie</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D36" s="2" t="str" cm="1">
+        <f t="array" ref="D36">_xlfn.XLOOKUP(C36,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.XLOOKUP(F36,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
         <v>Maëlan</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D37" s="2" t="str" cm="1">
+        <f t="array" ref="D37">_xlfn.XLOOKUP(C37,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str" cm="1">
+        <f t="array" ref="G37">_xlfn.XLOOKUP(F37,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
         <v>Maëlle</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D38" s="2" t="str" cm="1">
+        <f t="array" ref="D38">_xlfn.XLOOKUP(C38,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str" cm="1">
+        <f t="array" ref="G38">_xlfn.XLOOKUP(F38,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
         <v>Marius</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D39" s="2" t="str" cm="1">
+        <f t="array" ref="D39">_xlfn.XLOOKUP(C39,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str" cm="1">
+        <f t="array" ref="G39">_xlfn.XLOOKUP(F39,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
         <v>Marot</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D40" s="2" t="str" cm="1">
+        <f t="array" ref="D40">_xlfn.XLOOKUP(C40,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.XLOOKUP(F40,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
         <v>Mathis</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D41" s="2" t="str" cm="1">
+        <f t="array" ref="D41">_xlfn.XLOOKUP(C41,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.XLOOKUP(F41,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
         <v>Matteo</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D42" s="2" t="str" cm="1">
+        <f t="array" ref="D42">_xlfn.XLOOKUP(C42,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.XLOOKUP(F42,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
         <v>Maxime</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D43" s="2" t="str" cm="1">
+        <f t="array" ref="D43">_xlfn.XLOOKUP(C43,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.XLOOKUP(F43,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
         <v>Maya</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D44" s="2" t="str" cm="1">
+        <f t="array" ref="D44">_xlfn.XLOOKUP(C44,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.XLOOKUP(F44,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
         <v>Mickaël</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D45" s="2" t="str" cm="1">
+        <f t="array" ref="D45">_xlfn.XLOOKUP(C45,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.XLOOKUP(F45,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
         <v>Morgana</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D46" s="2" t="str" cm="1">
+        <f t="array" ref="D46">_xlfn.XLOOKUP(C46,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.XLOOKUP(F46,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
         <v>Morgane</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D47" s="2" t="str" cm="1">
+        <f t="array" ref="D47">_xlfn.XLOOKUP(C47,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.XLOOKUP(F47,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
         <v>Nathalia</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D48" s="2" t="str" cm="1">
+        <f t="array" ref="D48">_xlfn.XLOOKUP(C48,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.XLOOKUP(F48,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
         <v>Noah</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D49" s="2" t="str" cm="1">
+        <f t="array" ref="D49">_xlfn.XLOOKUP(C49,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.XLOOKUP(F49,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
         <v>Patrick</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D50" s="2" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(C50,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(F50,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
         <v>Rama</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D51" s="2" t="str" cm="1">
+        <f t="array" ref="D51">_xlfn.XLOOKUP(C51,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.XLOOKUP(F51,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
         <v>Raphaël</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D52" s="2" t="str" cm="1">
+        <f t="array" ref="D52">_xlfn.XLOOKUP(C52,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.XLOOKUP(F52,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
         <v>Raphaëlle</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D53" s="2" t="str" cm="1">
+        <f t="array" ref="D53">_xlfn.XLOOKUP(C53,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.XLOOKUP(F53,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
         <v>Roxanne</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D54" s="2" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(C54,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(F54,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
         <v>Sébastien</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D55" s="2" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(C55,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(F55,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
         <v>Simon</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D56" s="2" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(C56,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(F56,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
         <v>Theo</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D57" s="2" t="str" cm="1">
+        <f t="array" ref="D57">_xlfn.XLOOKUP(C57,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.XLOOKUP(F57,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
         <v>Thibault</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D58" s="2" t="str" cm="1">
+        <f t="array" ref="D58">_xlfn.XLOOKUP(C58,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.XLOOKUP(F58,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
         <v>Titouan</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D59" s="2" t="str" cm="1">
+        <f t="array" ref="D59">_xlfn.XLOOKUP(C59,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.XLOOKUP(F59,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
         <v>Tristan</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D60" s="2" t="str" cm="1">
+        <f t="array" ref="D60">_xlfn.XLOOKUP(C60,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.XLOOKUP(F60,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
         <v>Yann</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D61" s="2" t="str" cm="1">
+        <f t="array" ref="D61">_xlfn.XLOOKUP(C61,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.XLOOKUP(F61,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D62" s="2" t="str" cm="1">
+        <f t="array" ref="D62">_xlfn.XLOOKUP(C62,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.XLOOKUP(F62,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
         <v>Mireille</v>
       </c>
+      <c r="D63" s="2" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(C63,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(F63,Table6[Dimanche],Table6[[Début]:[Fin]],"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F1:F1048576" name="Concerts2"/>
+    <protectedRange sqref="C1:C1048576" name="Concerts1"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6875EF01-3F3E-45A7-BC92-0C7AD64098EE}">
-  <dimension ref="A1:H63"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="2" width="13.765625" customWidth="1"/>
-    <col min="3" max="3" width="11.53515625" customWidth="1"/>
-    <col min="4" max="5" width="8.765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.53515625" customWidth="1"/>
-    <col min="7" max="8" width="8.765625" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
-        <v>Bouvet</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Agathe</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" t="str">
-        <v>Bulka</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Alegria Lily</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="str">
-        <v>Bastian</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Alexandra</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="str">
-        <v>L'Horset</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Alice</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" t="str">
-        <v>Ledru</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Analou</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" t="str">
-        <v>Mallet</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Anna</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" t="str">
-        <v>Malric</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Annouk</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" t="str">
-        <v>Noël</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Antonin</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" t="str">
-        <v>Tessier</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Arsène</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" t="str">
-        <v>Uldry</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Arthur</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" t="str">
-        <v>Marchand</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Athénaé</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" t="str">
-        <v>Magerand</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Auxence</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" t="str">
-        <v>Baruch</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Ava</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" t="str">
-        <v>Detrain</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Benoît</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" t="str">
-        <v>Meige</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Corentin</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" t="str">
-        <v>De Filippo</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Emma</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" t="str">
-        <v>Maître</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Enzo</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" t="str">
-        <v>Prouvost</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Eugénie</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" t="str">
-        <v xml:space="preserve">Rakotonandrasana </v>
-      </c>
-      <c r="B20" t="str">
-        <v>Iris</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" t="str">
-        <v>Bürgisser</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Jamilah</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" t="str">
-        <v>Ruscio</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Jolan</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" t="str">
-        <v>Wuilloud</v>
-      </c>
-      <c r="B23" t="str">
-        <v xml:space="preserve">Jonas </v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" t="str">
-        <v>Pirolley</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Jules</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" t="str">
-        <v>Chavaillaz</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Julie</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" t="str">
-        <v>Oeschger</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Kristel</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" t="str">
-        <v>Baltzinger</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Léa</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" t="str">
-        <v>Chambaz</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Léa</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" t="str">
-        <v>Ledru</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Lina-Rosa</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" t="str">
-        <v>Jaquet</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Lisa</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" t="str">
-        <v>Magnin</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Lisa</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" t="str">
-        <v>Cardis</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Louis</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" t="str">
-        <v>Post</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Louis</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" t="str">
-        <v>Blanchard</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Louise</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" t="str">
-        <v>Chastroux</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Lucas</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" t="str">
-        <v>Meyer</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Lucie</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" t="str">
-        <v>Ménétrey</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Maëlan</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="str">
-        <v>Chambaz</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Maëlle</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" t="str">
-        <v>Felix</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Marius</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" t="str">
-        <v>Ledru</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Marot</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41" t="str">
-        <v>Cuinet</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Mathis</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42" t="str">
-        <v>Gavin</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Matteo</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43" t="str">
-        <v>Debray</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Maxime</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44" t="str">
-        <v>Corbelli</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Maya</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45" t="str">
-        <v>Pasche</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Mickaël</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46" t="str">
-        <v>Fargues</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Morgana</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47" t="str">
-        <v>Scyboz (Lambelet)</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Morgane</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48" t="str">
-        <v>Koux</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Nathalia</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A49" t="str">
-        <v>Cherpillod</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Noah</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A50" t="str">
-        <v>Chambaz</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Patrick</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A51" t="str">
-        <v>Assaoui</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Rama</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52" t="str">
-        <v>Lacroze</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Raphaël</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A53" t="str">
-        <v>Neidhart</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Raphaëlle</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A54" t="str">
-        <v xml:space="preserve">Lanni </v>
-      </c>
-      <c r="B54" t="str">
-        <v>Roxanne</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A55" t="str">
-        <v>Schiesser</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Sébastien</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A56" t="str">
-        <v>Lambelet</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Simon</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A57" t="str">
-        <v>Cyprien</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Theo</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A58" t="str">
-        <v>Clerici</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Thibault</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A59" t="str">
-        <v>Ménétrey</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Titouan</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A60" t="str">
-        <v>Clerici</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Tristan</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A61" t="str">
-        <v>Bally</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Yann</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A62" t="str">
-        <v>Ménétrey</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Ysatis</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A63" t="str">
-        <v>Ménard</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Mireille</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DD389C5C-12D0-48D9-8D2C-258FFA120C30}">
+          <x14:formula1>
+            <xm:f>Concerts!$P$2:$P$17</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C63 F2:F63</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163BC770-3B95-40DC-97C2-8529964DDCBE}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>

--- a/data/blocages.xlsx
+++ b/data/blocages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C761906-A988-4ABE-9FED-23B989B7BA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86924202-825D-41AD-815F-A4E20490BECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   <externalReferences>
     <externalReference r:id="rId8"/>
   </externalReferences>
-  <calcPr calcId="191029" iterate="1" iterateCount="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1627,6 +1627,16 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1"/>
+          <cell r="E1"/>
+          <cell r="F1"/>
+        </row>
+        <row r="2">
+          <cell r="B2"/>
+          <cell r="E2"/>
+          <cell r="F2"/>
+        </row>
         <row r="3">
           <cell r="B3" t="str">
             <v>In</v>
@@ -2390,6 +2400,7 @@
           <cell r="B72" t="b">
             <v>0</v>
           </cell>
+          <cell r="E72"/>
           <cell r="F72" t="str">
             <v>Michelle-Evy</v>
           </cell>
@@ -2618,6 +2629,7 @@
           <cell r="B93" t="b">
             <v>0</v>
           </cell>
+          <cell r="E93"/>
           <cell r="F93" t="str">
             <v>Ramón</v>
           </cell>
@@ -2632,6 +2644,11 @@
           <cell r="F94" t="str">
             <v>Robert</v>
           </cell>
+        </row>
+        <row r="95">
+          <cell r="B95"/>
+          <cell r="E95"/>
+          <cell r="F95"/>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
